--- a/Data/HIC.xlsx
+++ b/Data/HIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\5pira\Documents\NSS-DDA17\Projects\housing\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4508DC56-3E83-4C4C-9808-605CFAAF81F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8D7907-68AF-4620-AA82-491E51E75B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{CC613340-222B-472F-B156-E697467D3C46}"/>
+    <workbookView xWindow="19290" yWindow="75" windowWidth="19080" windowHeight="20925" xr2:uid="{CC613340-222B-472F-B156-E697467D3C46}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="124">
   <si>
     <t>Year</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>Ind_YR_SH</t>
+  </si>
+  <si>
+    <t>Family_RR</t>
+  </si>
+  <si>
+    <t>Ind_RR</t>
   </si>
 </sst>
 </file>
@@ -773,15 +779,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C72177E-A1CE-40FD-98F1-E6A2E9B9FC6A}">
-  <dimension ref="A1:J1009"/>
+  <dimension ref="A1:L1009"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -798,22 +804,28 @@
         <v>118</v>
       </c>
       <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
         <v>115</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>119</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>121</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>120</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2007</v>
       </c>
@@ -829,20 +841,20 @@
       <c r="E2">
         <v>877</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>953</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1313</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1730</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>1467</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2007</v>
       </c>
@@ -858,20 +870,20 @@
       <c r="E3">
         <v>234</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>73</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>657</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>429</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2007</v>
       </c>
@@ -882,7 +894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2007</v>
       </c>
@@ -898,20 +910,20 @@
       <c r="E5">
         <v>2978</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1066</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2049</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>2619</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>1953</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2007</v>
       </c>
@@ -927,20 +939,20 @@
       <c r="E6">
         <v>419</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>713</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>951</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>690</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>825</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2007</v>
       </c>
@@ -956,20 +968,20 @@
       <c r="E7">
         <v>15421</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>8913</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>13178</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>15476</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>17874</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2007</v>
       </c>
@@ -985,20 +997,20 @@
       <c r="E8">
         <v>2563</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>589</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1759</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>1071</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1521</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2007</v>
       </c>
@@ -1014,20 +1026,20 @@
       <c r="E9">
         <v>651</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1222</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1273</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>920</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>2282</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -1043,20 +1055,20 @@
       <c r="E10">
         <v>222</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>6</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>340</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>488</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>288</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2007</v>
       </c>
@@ -1072,20 +1084,20 @@
       <c r="E11">
         <v>1092</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1623</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>2285</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1171</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>2016</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2007</v>
       </c>
@@ -1101,20 +1113,20 @@
       <c r="E12">
         <v>5197</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>3416</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>5929</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>6952</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>4950</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2007</v>
       </c>
@@ -1130,20 +1142,20 @@
       <c r="E13">
         <v>2401</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1160</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>2800</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>2656</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1768</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2007</v>
       </c>
@@ -1159,20 +1171,20 @@
       <c r="E14">
         <v>60</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>17</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>48</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>78</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2007</v>
       </c>
@@ -1188,20 +1200,20 @@
       <c r="E15">
         <v>1333</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>109</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>487</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>686</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>735</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2007</v>
       </c>
@@ -1217,20 +1229,20 @@
       <c r="E16">
         <v>557</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>159</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>432</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>323</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2007</v>
       </c>
@@ -1246,20 +1258,20 @@
       <c r="E17">
         <v>5972</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>3270</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>3390</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>2676</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>5556</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2007</v>
       </c>
@@ -1275,20 +1287,20 @@
       <c r="E18">
         <v>2097</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>287</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>1888</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>2104</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>1582</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2007</v>
       </c>
@@ -1304,20 +1316,20 @@
       <c r="E19">
         <v>1471</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>456</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>796</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>744</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>372</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2007</v>
       </c>
@@ -1333,20 +1345,20 @@
       <c r="E20">
         <v>529</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>310</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>975</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>528</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2007</v>
       </c>
@@ -1362,20 +1374,20 @@
       <c r="E21">
         <v>2378</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>906</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1831</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1094</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>995</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2007</v>
       </c>
@@ -1391,20 +1403,20 @@
       <c r="E22">
         <v>1198</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>735</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>1071</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>1824</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>1418</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2007</v>
       </c>
@@ -1420,20 +1432,20 @@
       <c r="E23">
         <v>1367</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>540</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>576</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>663</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>774</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2007</v>
       </c>
@@ -1449,20 +1461,20 @@
       <c r="E24">
         <v>1997</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>2628</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1306</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1490</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>1660</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2007</v>
       </c>
@@ -1478,20 +1490,20 @@
       <c r="E25">
         <v>2265</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>2122</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>2900</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>3905</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>5810</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2007</v>
       </c>
@@ -1507,20 +1519,20 @@
       <c r="E26">
         <v>2991</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>2224</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>3855</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>2340</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>2803</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2007</v>
       </c>
@@ -1536,20 +1548,20 @@
       <c r="E27">
         <v>2891</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>2935</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>1516</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>912</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>2471</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2007</v>
       </c>
@@ -1565,20 +1577,20 @@
       <c r="E28">
         <v>246</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>65</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>543</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>640</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>203</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2007</v>
       </c>
@@ -1594,20 +1606,20 @@
       <c r="E29">
         <v>1707</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>2102</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>1667</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>1739</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>1765</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2007</v>
       </c>
@@ -1623,20 +1635,20 @@
       <c r="E30">
         <v>352</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>87</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>417</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>203</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>230</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2007</v>
       </c>
@@ -1652,20 +1664,20 @@
       <c r="E31">
         <v>1033</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>163</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>932</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>696</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2007</v>
       </c>
@@ -1681,20 +1693,20 @@
       <c r="E32">
         <v>1543</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>510</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>1601</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>2191</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>895</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2007</v>
       </c>
@@ -1710,20 +1722,20 @@
       <c r="E33">
         <v>601</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>263</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>358</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>285</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>393</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2007</v>
       </c>
@@ -1739,20 +1751,20 @@
       <c r="E34">
         <v>1582</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>781</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>2357</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>1563</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>1535</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2007</v>
       </c>
@@ -1768,20 +1780,20 @@
       <c r="E35">
         <v>582</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>232</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>695</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>361</v>
       </c>
-      <c r="J35">
+      <c r="L35">
         <v>588</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2007</v>
       </c>
@@ -1797,20 +1809,20 @@
       <c r="E36">
         <v>6025</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>11040</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>14545</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>8337</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>19206</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2007</v>
       </c>
@@ -1826,20 +1838,20 @@
       <c r="E37">
         <v>1616</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>900</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>3313</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>2690</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>1119</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -1855,20 +1867,20 @@
       <c r="E38">
         <v>139</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>202</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>344</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>203</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2007</v>
       </c>
@@ -1879,7 +1891,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2007</v>
       </c>
@@ -1895,20 +1907,20 @@
       <c r="E40">
         <v>2754</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3776</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>3991</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>2545</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>6726</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2007</v>
       </c>
@@ -1924,20 +1936,20 @@
       <c r="E41">
         <v>608</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>112</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>1351</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>708</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>383</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2007</v>
       </c>
@@ -1953,20 +1965,20 @@
       <c r="E42">
         <v>4406</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>3052</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>2624</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>4594</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>3889</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2007</v>
       </c>
@@ -1982,20 +1994,20 @@
       <c r="E43">
         <v>5979</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>5211</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>3383</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>3608</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>3983</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2007</v>
       </c>
@@ -2011,20 +2023,20 @@
       <c r="E44">
         <v>188</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>240</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>407</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>1828</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>797</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2007</v>
       </c>
@@ -2040,20 +2052,20 @@
       <c r="E45">
         <v>463</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>335</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>397</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>240</v>
       </c>
-      <c r="J45">
+      <c r="L45">
         <v>608</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2007</v>
       </c>
@@ -2069,20 +2081,20 @@
       <c r="E46">
         <v>782</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>352</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>970</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>1322</v>
       </c>
-      <c r="J46">
+      <c r="L46">
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2007</v>
       </c>
@@ -2098,20 +2110,20 @@
       <c r="E47">
         <v>218</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>101</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>311</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>481</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2007</v>
       </c>
@@ -2127,20 +2139,20 @@
       <c r="E48">
         <v>1305</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>1017</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>2206</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>1970</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>1486</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2007</v>
       </c>
@@ -2156,20 +2168,20 @@
       <c r="E49">
         <v>5317</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>2100</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>7726</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>3459</v>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>2788</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2007</v>
       </c>
@@ -2185,20 +2197,20 @@
       <c r="E50">
         <v>1051</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>485</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>844</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>637</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>849</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2007</v>
       </c>
@@ -2214,20 +2226,20 @@
       <c r="E51">
         <v>194</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>125</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>284</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>157</v>
       </c>
-      <c r="J51">
+      <c r="L51">
         <v>360</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2007</v>
       </c>
@@ -2243,20 +2255,20 @@
       <c r="E52">
         <v>4</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>19</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>69</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>45</v>
       </c>
-      <c r="J52">
+      <c r="L52">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2007</v>
       </c>
@@ -2272,20 +2284,20 @@
       <c r="E53">
         <v>2676</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>547</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>1796</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>1445</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>1344</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2007</v>
       </c>
@@ -2301,20 +2313,20 @@
       <c r="E54">
         <v>8128</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>1447</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>3811</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>2930</v>
       </c>
-      <c r="J54">
+      <c r="L54">
         <v>4163</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2007</v>
       </c>
@@ -2330,20 +2342,20 @@
       <c r="E55">
         <v>283</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>72</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>930</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>363</v>
       </c>
-      <c r="J55">
+      <c r="L55">
         <v>398</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2007</v>
       </c>
@@ -2359,20 +2371,20 @@
       <c r="E56">
         <v>2328</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>713</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>1401</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>900</v>
       </c>
-      <c r="J56">
+      <c r="L56">
         <v>1012</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2007</v>
       </c>
@@ -2388,20 +2400,20 @@
       <c r="E57">
         <v>97</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>0</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>286</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>128</v>
       </c>
-      <c r="J57">
+      <c r="L57">
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2008</v>
       </c>
@@ -2417,23 +2429,23 @@
       <c r="E58">
         <v>832</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>826</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>1145</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>34</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>1832</v>
       </c>
-      <c r="J58">
+      <c r="L58">
         <v>1589</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2008</v>
       </c>
@@ -2449,20 +2461,20 @@
       <c r="E59">
         <v>228</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>68</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>649</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>355</v>
       </c>
-      <c r="J59">
+      <c r="L59">
         <v>398</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2008</v>
       </c>
@@ -2473,7 +2485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2008</v>
       </c>
@@ -2489,23 +2501,23 @@
       <c r="E61">
         <v>3263</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>1078</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>2238</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>40</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>2256</v>
       </c>
-      <c r="J61">
+      <c r="L61">
         <v>2440</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2008</v>
       </c>
@@ -2521,20 +2533,20 @@
       <c r="E62">
         <v>332</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>667</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>662</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>522</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>845</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2008</v>
       </c>
@@ -2550,23 +2562,23 @@
       <c r="E63">
         <v>15812</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>9505</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>13310</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>202</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>16029</v>
       </c>
-      <c r="J63">
+      <c r="L63">
         <v>17598</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2008</v>
       </c>
@@ -2582,23 +2594,23 @@
       <c r="E64">
         <v>2589</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>709</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>1643</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>25</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>1164</v>
       </c>
-      <c r="J64">
+      <c r="L64">
         <v>1618</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2008</v>
       </c>
@@ -2614,20 +2626,20 @@
       <c r="E65">
         <v>746</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>1357</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>1257</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>878</v>
       </c>
-      <c r="J65">
+      <c r="L65">
         <v>2248</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2008</v>
       </c>
@@ -2643,23 +2655,23 @@
       <c r="E66">
         <v>291</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>30</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>359</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>10</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>377</v>
       </c>
-      <c r="J66">
+      <c r="L66">
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2008</v>
       </c>
@@ -2675,23 +2687,23 @@
       <c r="E67">
         <v>1523</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>1060</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>2642</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>25</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>1149</v>
       </c>
-      <c r="J67">
+      <c r="L67">
         <v>2056</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2008</v>
       </c>
@@ -2707,23 +2719,23 @@
       <c r="E68">
         <v>4873</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>3761</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>6181</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>203</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>7752</v>
       </c>
-      <c r="J68">
+      <c r="L68">
         <v>5229</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2008</v>
       </c>
@@ -2739,23 +2751,23 @@
       <c r="E69">
         <v>2585</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>1585</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>3123</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>15</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>2815</v>
       </c>
-      <c r="J69">
+      <c r="L69">
         <v>2199</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2008</v>
       </c>
@@ -2771,20 +2783,20 @@
       <c r="E70">
         <v>91</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>12</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>58</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>56</v>
       </c>
-      <c r="J70">
+      <c r="L70">
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2008</v>
       </c>
@@ -2800,23 +2812,23 @@
       <c r="E71">
         <v>1835</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>147</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>675</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>25</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>615</v>
       </c>
-      <c r="J71">
+      <c r="L71">
         <v>581</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2008</v>
       </c>
@@ -2832,20 +2844,20 @@
       <c r="E72">
         <v>576</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>167</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>514</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>414</v>
       </c>
-      <c r="J72">
+      <c r="L72">
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2008</v>
       </c>
@@ -2861,23 +2873,23 @@
       <c r="E73">
         <v>5967</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>3576</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>3518</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>131</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>2517</v>
       </c>
-      <c r="J73">
+      <c r="L73">
         <v>6251</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2008</v>
       </c>
@@ -2893,23 +2905,23 @@
       <c r="E74">
         <v>2349</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>540</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>1940</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>25</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>2353</v>
       </c>
-      <c r="J74">
+      <c r="L74">
         <v>1466</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2008</v>
       </c>
@@ -2925,20 +2937,20 @@
       <c r="E75">
         <v>1749</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>442</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>899</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>961</v>
       </c>
-      <c r="J75">
+      <c r="L75">
         <v>349</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2008</v>
       </c>
@@ -2954,23 +2966,23 @@
       <c r="E76">
         <v>467</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>286</v>
       </c>
-      <c r="G76">
+      <c r="H76">
         <v>796</v>
       </c>
-      <c r="H76">
+      <c r="I76">
         <v>20</v>
       </c>
-      <c r="I76">
+      <c r="J76">
         <v>452</v>
       </c>
-      <c r="J76">
+      <c r="L76">
         <v>432</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2008</v>
       </c>
@@ -2986,23 +2998,23 @@
       <c r="E77">
         <v>2109</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>865</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>1888</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>10</v>
       </c>
-      <c r="I77">
+      <c r="J77">
         <v>1190</v>
       </c>
-      <c r="J77">
+      <c r="L77">
         <v>1007</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2008</v>
       </c>
@@ -3018,23 +3030,23 @@
       <c r="E78">
         <v>1368</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>939</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>1015</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>25</v>
       </c>
-      <c r="I78">
+      <c r="J78">
         <v>1712</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>1491</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2008</v>
       </c>
@@ -3050,20 +3062,20 @@
       <c r="E79">
         <v>1241</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>797</v>
       </c>
-      <c r="G79">
+      <c r="H79">
         <v>609</v>
       </c>
-      <c r="I79">
+      <c r="J79">
         <v>717</v>
       </c>
-      <c r="J79">
+      <c r="L79">
         <v>955</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2008</v>
       </c>
@@ -3079,23 +3091,23 @@
       <c r="E80">
         <v>1724</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>2841</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>1202</v>
       </c>
-      <c r="H80">
+      <c r="I80">
         <v>104</v>
       </c>
-      <c r="I80">
+      <c r="J80">
         <v>1446</v>
       </c>
-      <c r="J80">
+      <c r="L80">
         <v>1761</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2008</v>
       </c>
@@ -3111,23 +3123,23 @@
       <c r="E81">
         <v>2222</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>2114</v>
       </c>
-      <c r="G81">
+      <c r="H81">
         <v>2826</v>
       </c>
-      <c r="H81">
+      <c r="I81">
         <v>37</v>
       </c>
-      <c r="I81">
+      <c r="J81">
         <v>3475</v>
       </c>
-      <c r="J81">
+      <c r="L81">
         <v>5986</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2008</v>
       </c>
@@ -3143,23 +3155,23 @@
       <c r="E82">
         <v>3212</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>3896</v>
       </c>
-      <c r="G82">
+      <c r="H82">
         <v>3485</v>
       </c>
-      <c r="H82">
+      <c r="I82">
         <v>43</v>
       </c>
-      <c r="I82">
+      <c r="J82">
         <v>2638</v>
       </c>
-      <c r="J82">
+      <c r="L82">
         <v>2987</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2008</v>
       </c>
@@ -3175,23 +3187,23 @@
       <c r="E83">
         <v>2781</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>3300</v>
       </c>
-      <c r="G83">
+      <c r="H83">
         <v>1510</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>10</v>
       </c>
-      <c r="I83">
+      <c r="J83">
         <v>938</v>
       </c>
-      <c r="J83">
+      <c r="L83">
         <v>2739</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2008</v>
       </c>
@@ -3207,20 +3219,20 @@
       <c r="E84">
         <v>268</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>62</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>547</v>
       </c>
-      <c r="I84">
+      <c r="J84">
         <v>657</v>
       </c>
-      <c r="J84">
+      <c r="L84">
         <v>194</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2008</v>
       </c>
@@ -3236,23 +3248,23 @@
       <c r="E85">
         <v>1994</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>1914</v>
       </c>
-      <c r="G85">
+      <c r="H85">
         <v>1900</v>
       </c>
-      <c r="H85">
+      <c r="I85">
         <v>26</v>
       </c>
-      <c r="I85">
+      <c r="J85">
         <v>1358</v>
       </c>
-      <c r="J85">
+      <c r="L85">
         <v>1047</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2008</v>
       </c>
@@ -3268,20 +3280,20 @@
       <c r="E86">
         <v>341</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>47</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>360</v>
       </c>
-      <c r="I86">
+      <c r="J86">
         <v>198</v>
       </c>
-      <c r="J86">
+      <c r="L86">
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2008</v>
       </c>
@@ -3297,20 +3309,20 @@
       <c r="E87">
         <v>943</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>25</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>844</v>
       </c>
-      <c r="I87">
+      <c r="J87">
         <v>729</v>
       </c>
-      <c r="J87">
+      <c r="L87">
         <v>221</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2008</v>
       </c>
@@ -3326,23 +3338,23 @@
       <c r="E88">
         <v>911</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>450</v>
       </c>
-      <c r="G88">
+      <c r="H88">
         <v>1301</v>
       </c>
-      <c r="H88">
+      <c r="I88">
         <v>25</v>
       </c>
-      <c r="I88">
+      <c r="J88">
         <v>2571</v>
       </c>
-      <c r="J88">
+      <c r="L88">
         <v>1418</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2008</v>
       </c>
@@ -3358,23 +3370,23 @@
       <c r="E89">
         <v>512</v>
       </c>
-      <c r="F89">
+      <c r="G89">
         <v>358</v>
       </c>
-      <c r="G89">
+      <c r="H89">
         <v>414</v>
       </c>
-      <c r="H89">
+      <c r="I89">
         <v>5</v>
       </c>
-      <c r="I89">
+      <c r="J89">
         <v>301</v>
       </c>
-      <c r="J89">
+      <c r="L89">
         <v>476</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2008</v>
       </c>
@@ -3390,23 +3402,23 @@
       <c r="E90">
         <v>1469</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>784</v>
       </c>
-      <c r="G90">
+      <c r="H90">
         <v>2523</v>
       </c>
-      <c r="H90">
+      <c r="I90">
         <v>29</v>
       </c>
-      <c r="I90">
+      <c r="J90">
         <v>1010</v>
       </c>
-      <c r="J90">
+      <c r="L90">
         <v>1663</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2008</v>
       </c>
@@ -3422,20 +3434,20 @@
       <c r="E91">
         <v>704</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>321</v>
       </c>
-      <c r="G91">
+      <c r="H91">
         <v>670</v>
       </c>
-      <c r="I91">
+      <c r="J91">
         <v>434</v>
       </c>
-      <c r="J91">
+      <c r="L91">
         <v>715</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2008</v>
       </c>
@@ -3451,23 +3463,23 @@
       <c r="E92">
         <v>5901</v>
       </c>
-      <c r="F92">
+      <c r="G92">
         <v>11068</v>
       </c>
-      <c r="G92">
+      <c r="H92">
         <v>12683</v>
       </c>
-      <c r="H92">
+      <c r="I92">
         <v>143</v>
       </c>
-      <c r="I92">
+      <c r="J92">
         <v>7099</v>
       </c>
-      <c r="J92">
+      <c r="L92">
         <v>20713</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -3483,20 +3495,20 @@
       <c r="E93">
         <v>1901</v>
       </c>
-      <c r="F93">
+      <c r="G93">
         <v>1056</v>
       </c>
-      <c r="G93">
+      <c r="H93">
         <v>3597</v>
       </c>
-      <c r="I93">
+      <c r="J93">
         <v>2560</v>
       </c>
-      <c r="J93">
+      <c r="L93">
         <v>1212</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2008</v>
       </c>
@@ -3512,20 +3524,20 @@
       <c r="E94">
         <v>101</v>
       </c>
-      <c r="F94">
+      <c r="G94">
         <v>212</v>
       </c>
-      <c r="G94">
+      <c r="H94">
         <v>357</v>
       </c>
-      <c r="I94">
+      <c r="J94">
         <v>114</v>
       </c>
-      <c r="J94">
+      <c r="L94">
         <v>205</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2008</v>
       </c>
@@ -3536,7 +3548,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2008</v>
       </c>
@@ -3552,23 +3564,23 @@
       <c r="E96">
         <v>2140</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>3320</v>
       </c>
-      <c r="G96">
+      <c r="H96">
         <v>4181</v>
       </c>
-      <c r="H96">
+      <c r="I96">
         <v>130</v>
       </c>
-      <c r="I96">
+      <c r="J96">
         <v>2005</v>
       </c>
-      <c r="J96">
+      <c r="L96">
         <v>6291</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2008</v>
       </c>
@@ -3584,23 +3596,23 @@
       <c r="E97">
         <v>504</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>119</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>1532</v>
       </c>
-      <c r="H97">
+      <c r="I97">
         <v>50</v>
       </c>
-      <c r="I97">
+      <c r="J97">
         <v>690</v>
       </c>
-      <c r="J97">
+      <c r="L97">
         <v>308</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2008</v>
       </c>
@@ -3616,23 +3628,23 @@
       <c r="E98">
         <v>3197</v>
       </c>
-      <c r="F98">
+      <c r="G98">
         <v>2270</v>
       </c>
-      <c r="G98">
+      <c r="H98">
         <v>2291</v>
       </c>
-      <c r="H98">
+      <c r="I98">
         <v>59</v>
       </c>
-      <c r="I98">
+      <c r="J98">
         <v>2260</v>
       </c>
-      <c r="J98">
+      <c r="L98">
         <v>2708</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2008</v>
       </c>
@@ -3648,23 +3660,23 @@
       <c r="E99">
         <v>6321</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>5164</v>
       </c>
-      <c r="G99">
+      <c r="H99">
         <v>3681</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>141</v>
       </c>
-      <c r="I99">
+      <c r="J99">
         <v>3105</v>
       </c>
-      <c r="J99">
+      <c r="L99">
         <v>3570</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2008</v>
       </c>
@@ -3680,23 +3692,23 @@
       <c r="E100">
         <v>218</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>228</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>343</v>
       </c>
-      <c r="H100">
+      <c r="I100">
         <v>22</v>
       </c>
-      <c r="I100">
+      <c r="J100">
         <v>1181</v>
       </c>
-      <c r="J100">
+      <c r="L100">
         <v>825</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2008</v>
       </c>
@@ -3712,23 +3724,23 @@
       <c r="E101">
         <v>247</v>
       </c>
-      <c r="F101">
+      <c r="G101">
         <v>569</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>499</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>17</v>
       </c>
-      <c r="I101">
+      <c r="J101">
         <v>161</v>
       </c>
-      <c r="J101">
+      <c r="L101">
         <v>626</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2008</v>
       </c>
@@ -3744,23 +3756,23 @@
       <c r="E102">
         <v>830</v>
       </c>
-      <c r="F102">
+      <c r="G102">
         <v>428</v>
       </c>
-      <c r="G102">
+      <c r="H102">
         <v>954</v>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>12</v>
       </c>
-      <c r="I102">
+      <c r="J102">
         <v>1327</v>
       </c>
-      <c r="J102">
+      <c r="L102">
         <v>561</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2008</v>
       </c>
@@ -3776,20 +3788,20 @@
       <c r="E103">
         <v>238</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>85</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>311</v>
       </c>
-      <c r="I103">
+      <c r="J103">
         <v>425</v>
       </c>
-      <c r="J103">
+      <c r="L103">
         <v>172</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2008</v>
       </c>
@@ -3805,23 +3817,23 @@
       <c r="E104">
         <v>1312</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>1028</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>2146</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>16</v>
       </c>
-      <c r="I104">
+      <c r="J104">
         <v>1929</v>
       </c>
-      <c r="J104">
+      <c r="L104">
         <v>1598</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2008</v>
       </c>
@@ -3837,23 +3849,23 @@
       <c r="E105">
         <v>5179</v>
       </c>
-      <c r="F105">
+      <c r="G105">
         <v>2559</v>
       </c>
-      <c r="G105">
+      <c r="H105">
         <v>8074</v>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>150</v>
       </c>
-      <c r="I105">
+      <c r="J105">
         <v>3014</v>
       </c>
-      <c r="J105">
+      <c r="L105">
         <v>3248</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2008</v>
       </c>
@@ -3869,23 +3881,23 @@
       <c r="E106">
         <v>1032</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>533</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>796</v>
       </c>
-      <c r="H106">
+      <c r="I106">
         <v>49</v>
       </c>
-      <c r="I106">
+      <c r="J106">
         <v>669</v>
       </c>
-      <c r="J106">
+      <c r="L106">
         <v>1092</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2008</v>
       </c>
@@ -3901,23 +3913,23 @@
       <c r="E107">
         <v>231</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>190</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>233</v>
       </c>
-      <c r="H107">
+      <c r="I107">
         <v>6</v>
       </c>
-      <c r="I107">
+      <c r="J107">
         <v>223</v>
       </c>
-      <c r="J107">
+      <c r="L107">
         <v>374</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2008</v>
       </c>
@@ -3933,20 +3945,20 @@
       <c r="E108">
         <v>4</v>
       </c>
-      <c r="F108">
+      <c r="G108">
         <v>21</v>
       </c>
-      <c r="G108">
+      <c r="H108">
         <v>28</v>
       </c>
-      <c r="I108">
+      <c r="J108">
         <v>46</v>
       </c>
-      <c r="J108">
+      <c r="L108">
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2008</v>
       </c>
@@ -3962,23 +3974,23 @@
       <c r="E109">
         <v>2750</v>
       </c>
-      <c r="F109">
+      <c r="G109">
         <v>580</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>1784</v>
       </c>
-      <c r="H109">
+      <c r="I109">
         <v>49</v>
       </c>
-      <c r="I109">
+      <c r="J109">
         <v>1264</v>
       </c>
-      <c r="J109">
+      <c r="L109">
         <v>1291</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2008</v>
       </c>
@@ -3994,23 +4006,23 @@
       <c r="E110">
         <v>8211</v>
       </c>
-      <c r="F110">
+      <c r="G110">
         <v>1737</v>
       </c>
-      <c r="G110">
+      <c r="H110">
         <v>3733</v>
       </c>
-      <c r="H110">
+      <c r="I110">
         <v>45</v>
       </c>
-      <c r="I110">
+      <c r="J110">
         <v>2778</v>
       </c>
-      <c r="J110">
+      <c r="L110">
         <v>4107</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2008</v>
       </c>
@@ -4026,23 +4038,23 @@
       <c r="E111">
         <v>335</v>
       </c>
-      <c r="F111">
+      <c r="G111">
         <v>117</v>
       </c>
-      <c r="G111">
+      <c r="H111">
         <v>896</v>
       </c>
-      <c r="H111">
+      <c r="I111">
         <v>12</v>
       </c>
-      <c r="I111">
+      <c r="J111">
         <v>370</v>
       </c>
-      <c r="J111">
+      <c r="L111">
         <v>409</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2008</v>
       </c>
@@ -4058,23 +4070,23 @@
       <c r="E112">
         <v>2286</v>
       </c>
-      <c r="F112">
+      <c r="G112">
         <v>768</v>
       </c>
-      <c r="G112">
+      <c r="H112">
         <v>1419</v>
       </c>
-      <c r="H112">
+      <c r="I112">
         <v>64</v>
       </c>
-      <c r="I112">
+      <c r="J112">
         <v>904</v>
       </c>
-      <c r="J112">
+      <c r="L112">
         <v>1182</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2008</v>
       </c>
@@ -4090,20 +4102,20 @@
       <c r="E113">
         <v>128</v>
       </c>
-      <c r="F113">
+      <c r="G113">
         <v>0</v>
       </c>
-      <c r="G113">
+      <c r="H113">
         <v>278</v>
       </c>
-      <c r="I113">
+      <c r="J113">
         <v>94</v>
       </c>
-      <c r="J113">
+      <c r="L113">
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2009</v>
       </c>
@@ -4119,23 +4131,23 @@
       <c r="E114">
         <v>844</v>
       </c>
-      <c r="F114">
+      <c r="G114">
         <v>771</v>
       </c>
-      <c r="G114">
+      <c r="H114">
         <v>1106</v>
       </c>
-      <c r="H114">
+      <c r="I114">
         <v>34</v>
       </c>
-      <c r="I114">
+      <c r="J114">
         <v>1576</v>
       </c>
-      <c r="J114">
+      <c r="L114">
         <v>1363</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2009</v>
       </c>
@@ -4151,20 +4163,20 @@
       <c r="E115">
         <v>209</v>
       </c>
-      <c r="F115">
+      <c r="G115">
         <v>93</v>
       </c>
-      <c r="G115">
+      <c r="H115">
         <v>673</v>
       </c>
-      <c r="I115">
+      <c r="J115">
         <v>373</v>
       </c>
-      <c r="J115">
+      <c r="L115">
         <v>414</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2009</v>
       </c>
@@ -4175,7 +4187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2009</v>
       </c>
@@ -4191,23 +4203,23 @@
       <c r="E117">
         <v>3373</v>
       </c>
-      <c r="F117">
+      <c r="G117">
         <v>1347</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>1994</v>
       </c>
-      <c r="H117">
+      <c r="I117">
         <v>40</v>
       </c>
-      <c r="I117">
+      <c r="J117">
         <v>1642</v>
       </c>
-      <c r="J117">
+      <c r="L117">
         <v>2579</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2009</v>
       </c>
@@ -4223,20 +4235,20 @@
       <c r="E118">
         <v>315</v>
       </c>
-      <c r="F118">
+      <c r="G118">
         <v>667</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>615</v>
       </c>
-      <c r="I118">
+      <c r="J118">
         <v>583</v>
       </c>
-      <c r="J118">
+      <c r="L118">
         <v>897</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2009</v>
       </c>
@@ -4252,23 +4264,23 @@
       <c r="E119">
         <v>15607</v>
       </c>
-      <c r="F119">
+      <c r="G119">
         <v>15161</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>13236</v>
       </c>
-      <c r="H119">
+      <c r="I119">
         <v>207</v>
       </c>
-      <c r="I119">
+      <c r="J119">
         <v>16362</v>
       </c>
-      <c r="J119">
+      <c r="L119">
         <v>21130</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2009</v>
       </c>
@@ -4284,23 +4296,23 @@
       <c r="E120">
         <v>2323</v>
       </c>
-      <c r="F120">
+      <c r="G120">
         <v>645</v>
       </c>
-      <c r="G120">
+      <c r="H120">
         <v>1580</v>
       </c>
-      <c r="H120">
+      <c r="I120">
         <v>25</v>
       </c>
-      <c r="I120">
+      <c r="J120">
         <v>1286</v>
       </c>
-      <c r="J120">
+      <c r="L120">
         <v>1705</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2009</v>
       </c>
@@ -4316,20 +4328,20 @@
       <c r="E121">
         <v>798</v>
       </c>
-      <c r="F121">
+      <c r="G121">
         <v>1578</v>
       </c>
-      <c r="G121">
+      <c r="H121">
         <v>1284</v>
       </c>
-      <c r="I121">
+      <c r="J121">
         <v>889</v>
       </c>
-      <c r="J121">
+      <c r="L121">
         <v>2491</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2009</v>
       </c>
@@ -4345,23 +4357,23 @@
       <c r="E122">
         <v>310</v>
       </c>
-      <c r="F122">
+      <c r="G122">
         <v>30</v>
       </c>
-      <c r="G122">
+      <c r="H122">
         <v>316</v>
       </c>
-      <c r="H122">
+      <c r="I122">
         <v>10</v>
       </c>
-      <c r="I122">
+      <c r="J122">
         <v>361</v>
       </c>
-      <c r="J122">
+      <c r="L122">
         <v>261</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2009</v>
       </c>
@@ -4377,23 +4389,23 @@
       <c r="E123">
         <v>1888</v>
       </c>
-      <c r="F123">
+      <c r="G123">
         <v>1165</v>
       </c>
-      <c r="G123">
+      <c r="H123">
         <v>2470</v>
       </c>
-      <c r="H123">
+      <c r="I123">
         <v>25</v>
       </c>
-      <c r="I123">
+      <c r="J123">
         <v>1220</v>
       </c>
-      <c r="J123">
+      <c r="L123">
         <v>2724</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2009</v>
       </c>
@@ -4409,23 +4421,23 @@
       <c r="E124">
         <v>5363</v>
       </c>
-      <c r="F124">
+      <c r="G124">
         <v>3917</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>6026</v>
       </c>
-      <c r="H124">
+      <c r="I124">
         <v>180</v>
       </c>
-      <c r="I124">
+      <c r="J124">
         <v>7561</v>
       </c>
-      <c r="J124">
+      <c r="L124">
         <v>5569</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2009</v>
       </c>
@@ -4441,20 +4453,20 @@
       <c r="E125">
         <v>2541</v>
       </c>
-      <c r="F125">
+      <c r="G125">
         <v>1694</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>3264</v>
       </c>
-      <c r="I125">
+      <c r="J125">
         <v>3101</v>
       </c>
-      <c r="J125">
+      <c r="L125">
         <v>2396</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2009</v>
       </c>
@@ -4470,20 +4482,20 @@
       <c r="E126">
         <v>88</v>
       </c>
-      <c r="F126">
+      <c r="G126">
         <v>13</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>54</v>
       </c>
-      <c r="I126">
+      <c r="J126">
         <v>53</v>
       </c>
-      <c r="J126">
+      <c r="L126">
         <v>47</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2009</v>
       </c>
@@ -4499,23 +4511,23 @@
       <c r="E127">
         <v>2179</v>
       </c>
-      <c r="F127">
+      <c r="G127">
         <v>239</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>524</v>
       </c>
-      <c r="H127">
+      <c r="I127">
         <v>25</v>
       </c>
-      <c r="I127">
+      <c r="J127">
         <v>754</v>
       </c>
-      <c r="J127">
+      <c r="L127">
         <v>692</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2009</v>
       </c>
@@ -4531,20 +4543,20 @@
       <c r="E128">
         <v>639</v>
       </c>
-      <c r="F128">
+      <c r="G128">
         <v>181</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>501</v>
       </c>
-      <c r="I128">
+      <c r="J128">
         <v>399</v>
       </c>
-      <c r="J128">
+      <c r="L128">
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2009</v>
       </c>
@@ -4560,23 +4572,23 @@
       <c r="E129">
         <v>5746</v>
       </c>
-      <c r="F129">
+      <c r="G129">
         <v>3449</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>3202</v>
       </c>
-      <c r="H129">
+      <c r="I129">
         <v>131</v>
       </c>
-      <c r="I129">
+      <c r="J129">
         <v>2474</v>
       </c>
-      <c r="J129">
+      <c r="L129">
         <v>6761</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2009</v>
       </c>
@@ -4592,23 +4604,23 @@
       <c r="E130">
         <v>1894</v>
       </c>
-      <c r="F130">
+      <c r="G130">
         <v>604</v>
       </c>
-      <c r="G130">
+      <c r="H130">
         <v>1866</v>
       </c>
-      <c r="H130">
+      <c r="I130">
         <v>25</v>
       </c>
-      <c r="I130">
+      <c r="J130">
         <v>2102</v>
       </c>
-      <c r="J130">
+      <c r="L130">
         <v>1265</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2009</v>
       </c>
@@ -4624,20 +4636,20 @@
       <c r="E131">
         <v>1794</v>
       </c>
-      <c r="F131">
+      <c r="G131">
         <v>399</v>
       </c>
-      <c r="G131">
+      <c r="H131">
         <v>944</v>
       </c>
-      <c r="I131">
+      <c r="J131">
         <v>908</v>
       </c>
-      <c r="J131">
+      <c r="L131">
         <v>392</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2009</v>
       </c>
@@ -4653,23 +4665,23 @@
       <c r="E132">
         <v>393</v>
       </c>
-      <c r="F132">
+      <c r="G132">
         <v>269</v>
       </c>
-      <c r="G132">
+      <c r="H132">
         <v>455</v>
       </c>
-      <c r="H132">
+      <c r="I132">
         <v>20</v>
       </c>
-      <c r="I132">
+      <c r="J132">
         <v>169</v>
       </c>
-      <c r="J132">
+      <c r="L132">
         <v>426</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2009</v>
       </c>
@@ -4685,23 +4697,23 @@
       <c r="E133">
         <v>1669</v>
       </c>
-      <c r="F133">
+      <c r="G133">
         <v>1183</v>
       </c>
-      <c r="G133">
+      <c r="H133">
         <v>1769</v>
       </c>
-      <c r="H133">
+      <c r="I133">
         <v>10</v>
       </c>
-      <c r="I133">
+      <c r="J133">
         <v>1003</v>
       </c>
-      <c r="J133">
+      <c r="L133">
         <v>1438</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2009</v>
       </c>
@@ -4717,23 +4729,23 @@
       <c r="E134">
         <v>1259</v>
       </c>
-      <c r="F134">
+      <c r="G134">
         <v>1038</v>
       </c>
-      <c r="G134">
+      <c r="H134">
         <v>1202</v>
       </c>
-      <c r="H134">
+      <c r="I134">
         <v>37</v>
       </c>
-      <c r="I134">
+      <c r="J134">
         <v>1786</v>
       </c>
-      <c r="J134">
+      <c r="L134">
         <v>1525</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2009</v>
       </c>
@@ -4749,20 +4761,20 @@
       <c r="E135">
         <v>1152</v>
       </c>
-      <c r="F135">
+      <c r="G135">
         <v>782</v>
       </c>
-      <c r="G135">
+      <c r="H135">
         <v>573</v>
       </c>
-      <c r="I135">
+      <c r="J135">
         <v>627</v>
       </c>
-      <c r="J135">
+      <c r="L135">
         <v>1014</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2009</v>
       </c>
@@ -4778,23 +4790,23 @@
       <c r="E136">
         <v>1693</v>
       </c>
-      <c r="F136">
+      <c r="G136">
         <v>2857</v>
       </c>
-      <c r="G136">
+      <c r="H136">
         <v>1497</v>
       </c>
-      <c r="H136">
+      <c r="I136">
         <v>104</v>
       </c>
-      <c r="I136">
+      <c r="J136">
         <v>1526</v>
       </c>
-      <c r="J136">
+      <c r="L136">
         <v>1918</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2009</v>
       </c>
@@ -4810,23 +4822,23 @@
       <c r="E137">
         <v>2140</v>
       </c>
-      <c r="F137">
+      <c r="G137">
         <v>2126</v>
       </c>
-      <c r="G137">
+      <c r="H137">
         <v>2837</v>
       </c>
-      <c r="H137">
+      <c r="I137">
         <v>37</v>
       </c>
-      <c r="I137">
+      <c r="J137">
         <v>3160</v>
       </c>
-      <c r="J137">
+      <c r="L137">
         <v>6214</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2009</v>
       </c>
@@ -4842,23 +4854,23 @@
       <c r="E138">
         <v>3814</v>
       </c>
-      <c r="F138">
+      <c r="G138">
         <v>5451</v>
       </c>
-      <c r="G138">
+      <c r="H138">
         <v>3234</v>
       </c>
-      <c r="H138">
+      <c r="I138">
         <v>43</v>
       </c>
-      <c r="I138">
+      <c r="J138">
         <v>2602</v>
       </c>
-      <c r="J138">
+      <c r="L138">
         <v>4131</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2009</v>
       </c>
@@ -4874,23 +4886,23 @@
       <c r="E139">
         <v>2793</v>
       </c>
-      <c r="F139">
+      <c r="G139">
         <v>4072</v>
       </c>
-      <c r="G139">
+      <c r="H139">
         <v>1569</v>
       </c>
-      <c r="H139">
+      <c r="I139">
         <v>10</v>
       </c>
-      <c r="I139">
+      <c r="J139">
         <v>912</v>
       </c>
-      <c r="J139">
+      <c r="L139">
         <v>3002</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2009</v>
       </c>
@@ -4906,20 +4918,20 @@
       <c r="E140">
         <v>256</v>
       </c>
-      <c r="F140">
+      <c r="G140">
         <v>77</v>
       </c>
-      <c r="G140">
+      <c r="H140">
         <v>505</v>
       </c>
-      <c r="I140">
+      <c r="J140">
         <v>392</v>
       </c>
-      <c r="J140">
+      <c r="L140">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2009</v>
       </c>
@@ -4935,23 +4947,23 @@
       <c r="E141">
         <v>2078</v>
       </c>
-      <c r="F141">
+      <c r="G141">
         <v>1841</v>
       </c>
-      <c r="G141">
+      <c r="H141">
         <v>1924</v>
       </c>
-      <c r="H141">
+      <c r="I141">
         <v>26</v>
       </c>
-      <c r="I141">
+      <c r="J141">
         <v>3633</v>
       </c>
-      <c r="J141">
+      <c r="L141">
         <v>3195</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2009</v>
       </c>
@@ -4967,20 +4979,20 @@
       <c r="E142">
         <v>331</v>
       </c>
-      <c r="F142">
+      <c r="G142">
         <v>47</v>
       </c>
-      <c r="G142">
+      <c r="H142">
         <v>367</v>
       </c>
-      <c r="I142">
+      <c r="J142">
         <v>227</v>
       </c>
-      <c r="J142">
+      <c r="L142">
         <v>177</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2009</v>
       </c>
@@ -4996,20 +5008,20 @@
       <c r="E143">
         <v>981</v>
       </c>
-      <c r="F143">
+      <c r="G143">
         <v>222</v>
       </c>
-      <c r="G143">
+      <c r="H143">
         <v>833</v>
       </c>
-      <c r="I143">
+      <c r="J143">
         <v>715</v>
       </c>
-      <c r="J143">
+      <c r="L143">
         <v>353</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2009</v>
       </c>
@@ -5025,23 +5037,23 @@
       <c r="E144">
         <v>1634</v>
       </c>
-      <c r="F144">
+      <c r="G144">
         <v>325</v>
       </c>
-      <c r="G144">
+      <c r="H144">
         <v>903</v>
       </c>
-      <c r="H144">
+      <c r="I144">
         <v>25</v>
       </c>
-      <c r="I144">
+      <c r="J144">
         <v>5221</v>
       </c>
-      <c r="J144">
+      <c r="L144">
         <v>1469</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2009</v>
       </c>
@@ -5057,23 +5069,23 @@
       <c r="E145">
         <v>426</v>
       </c>
-      <c r="F145">
+      <c r="G145">
         <v>410</v>
       </c>
-      <c r="G145">
+      <c r="H145">
         <v>372</v>
       </c>
-      <c r="H145">
+      <c r="I145">
         <v>9</v>
       </c>
-      <c r="I145">
+      <c r="J145">
         <v>249</v>
       </c>
-      <c r="J145">
+      <c r="L145">
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2009</v>
       </c>
@@ -5089,23 +5101,23 @@
       <c r="E146">
         <v>1488</v>
       </c>
-      <c r="F146">
+      <c r="G146">
         <v>765</v>
       </c>
-      <c r="G146">
+      <c r="H146">
         <v>2233</v>
       </c>
-      <c r="H146">
+      <c r="I146">
         <v>28</v>
       </c>
-      <c r="I146">
+      <c r="J146">
         <v>1045</v>
       </c>
-      <c r="J146">
+      <c r="L146">
         <v>1819</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2009</v>
       </c>
@@ -5121,20 +5133,20 @@
       <c r="E147">
         <v>712</v>
       </c>
-      <c r="F147">
+      <c r="G147">
         <v>403</v>
       </c>
-      <c r="G147">
+      <c r="H147">
         <v>770</v>
       </c>
-      <c r="I147">
+      <c r="J147">
         <v>541</v>
       </c>
-      <c r="J147">
+      <c r="L147">
         <v>745</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2009</v>
       </c>
@@ -5150,23 +5162,23 @@
       <c r="E148">
         <v>4823</v>
       </c>
-      <c r="F148">
+      <c r="G148">
         <v>12628</v>
       </c>
-      <c r="G148">
+      <c r="H148">
         <v>12770</v>
       </c>
-      <c r="H148">
+      <c r="I148">
         <v>124</v>
       </c>
-      <c r="I148">
+      <c r="J148">
         <v>7951</v>
       </c>
-      <c r="J148">
+      <c r="L148">
         <v>21751</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2009</v>
       </c>
@@ -5182,20 +5194,20 @@
       <c r="E149">
         <v>1704</v>
       </c>
-      <c r="F149">
+      <c r="G149">
         <v>1397</v>
       </c>
-      <c r="G149">
+      <c r="H149">
         <v>3457</v>
       </c>
-      <c r="I149">
+      <c r="J149">
         <v>2716</v>
       </c>
-      <c r="J149">
+      <c r="L149">
         <v>1571</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2009</v>
       </c>
@@ -5211,20 +5223,20 @@
       <c r="E150">
         <v>97</v>
       </c>
-      <c r="F150">
+      <c r="G150">
         <v>209</v>
       </c>
-      <c r="G150">
+      <c r="H150">
         <v>363</v>
       </c>
-      <c r="I150">
+      <c r="J150">
         <v>96</v>
       </c>
-      <c r="J150">
+      <c r="L150">
         <v>267</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2009</v>
       </c>
@@ -5235,7 +5247,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2009</v>
       </c>
@@ -5251,23 +5263,23 @@
       <c r="E152">
         <v>2211</v>
       </c>
-      <c r="F152">
+      <c r="G152">
         <v>3587</v>
       </c>
-      <c r="G152">
+      <c r="H152">
         <v>4210</v>
       </c>
-      <c r="H152">
+      <c r="I152">
         <v>130</v>
       </c>
-      <c r="I152">
+      <c r="J152">
         <v>2092</v>
       </c>
-      <c r="J152">
+      <c r="L152">
         <v>7313</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2009</v>
       </c>
@@ -5283,23 +5295,23 @@
       <c r="E153">
         <v>580</v>
       </c>
-      <c r="F153">
+      <c r="G153">
         <v>139</v>
       </c>
-      <c r="G153">
+      <c r="H153">
         <v>1689</v>
       </c>
-      <c r="H153">
+      <c r="I153">
         <v>50</v>
       </c>
-      <c r="I153">
+      <c r="J153">
         <v>526</v>
       </c>
-      <c r="J153">
+      <c r="L153">
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2009</v>
       </c>
@@ -5315,23 +5327,23 @@
       <c r="E154">
         <v>2688</v>
       </c>
-      <c r="F154">
+      <c r="G154">
         <v>2740</v>
       </c>
-      <c r="G154">
+      <c r="H154">
         <v>2144</v>
       </c>
-      <c r="H154">
+      <c r="I154">
         <v>43</v>
       </c>
-      <c r="I154">
+      <c r="J154">
         <v>2310</v>
       </c>
-      <c r="J154">
+      <c r="L154">
         <v>3244</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2009</v>
       </c>
@@ -5347,23 +5359,23 @@
       <c r="E155">
         <v>5917</v>
       </c>
-      <c r="F155">
+      <c r="G155">
         <v>3905</v>
       </c>
-      <c r="G155">
+      <c r="H155">
         <v>4264</v>
       </c>
-      <c r="H155">
+      <c r="I155">
         <v>158</v>
       </c>
-      <c r="I155">
+      <c r="J155">
         <v>2395</v>
       </c>
-      <c r="J155">
+      <c r="L155">
         <v>3731</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2009</v>
       </c>
@@ -5379,23 +5391,23 @@
       <c r="E156">
         <v>215</v>
       </c>
-      <c r="F156">
+      <c r="G156">
         <v>280</v>
       </c>
-      <c r="G156">
+      <c r="H156">
         <v>369</v>
       </c>
-      <c r="H156">
+      <c r="I156">
         <v>50</v>
       </c>
-      <c r="I156">
+      <c r="J156">
         <v>1283</v>
       </c>
-      <c r="J156">
+      <c r="L156">
         <v>739</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2009</v>
       </c>
@@ -5411,23 +5423,23 @@
       <c r="E157">
         <v>356</v>
       </c>
-      <c r="F157">
+      <c r="G157">
         <v>641</v>
       </c>
-      <c r="G157">
+      <c r="H157">
         <v>533</v>
       </c>
-      <c r="H157">
+      <c r="I157">
         <v>17</v>
       </c>
-      <c r="I157">
+      <c r="J157">
         <v>205</v>
       </c>
-      <c r="J157">
+      <c r="L157">
         <v>646</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2009</v>
       </c>
@@ -5443,23 +5455,23 @@
       <c r="E158">
         <v>975</v>
       </c>
-      <c r="F158">
+      <c r="G158">
         <v>446</v>
       </c>
-      <c r="G158">
+      <c r="H158">
         <v>932</v>
       </c>
-      <c r="H158">
+      <c r="I158">
         <v>12</v>
       </c>
-      <c r="I158">
+      <c r="J158">
         <v>1530</v>
       </c>
-      <c r="J158">
+      <c r="L158">
         <v>754</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2009</v>
       </c>
@@ -5475,20 +5487,20 @@
       <c r="E159">
         <v>238</v>
       </c>
-      <c r="F159">
+      <c r="G159">
         <v>85</v>
       </c>
-      <c r="G159">
+      <c r="H159">
         <v>311</v>
       </c>
-      <c r="I159">
+      <c r="J159">
         <v>425</v>
       </c>
-      <c r="J159">
+      <c r="L159">
         <v>172</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2009</v>
       </c>
@@ -5504,23 +5516,23 @@
       <c r="E160">
         <v>1146</v>
       </c>
-      <c r="F160">
+      <c r="G160">
         <v>747</v>
       </c>
-      <c r="G160">
+      <c r="H160">
         <v>1980</v>
       </c>
-      <c r="H160">
+      <c r="I160">
         <v>16</v>
       </c>
-      <c r="I160">
+      <c r="J160">
         <v>1763</v>
       </c>
-      <c r="J160">
+      <c r="L160">
         <v>1700</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2009</v>
       </c>
@@ -5536,23 +5548,23 @@
       <c r="E161">
         <v>5140</v>
       </c>
-      <c r="F161">
+      <c r="G161">
         <v>2546</v>
       </c>
-      <c r="G161">
+      <c r="H161">
         <v>8404</v>
       </c>
-      <c r="H161">
+      <c r="I161">
         <v>145</v>
       </c>
-      <c r="I161">
+      <c r="J161">
         <v>4201</v>
       </c>
-      <c r="J161">
+      <c r="L161">
         <v>3655</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2009</v>
       </c>
@@ -5568,23 +5580,23 @@
       <c r="E162">
         <v>977</v>
       </c>
-      <c r="F162">
+      <c r="G162">
         <v>584</v>
       </c>
-      <c r="G162">
+      <c r="H162">
         <v>821</v>
       </c>
-      <c r="H162">
+      <c r="I162">
         <v>49</v>
       </c>
-      <c r="I162">
+      <c r="J162">
         <v>698</v>
       </c>
-      <c r="J162">
+      <c r="L162">
         <v>894</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2009</v>
       </c>
@@ -5600,23 +5612,23 @@
       <c r="E163">
         <v>170</v>
       </c>
-      <c r="F163">
+      <c r="G163">
         <v>133</v>
       </c>
-      <c r="G163">
+      <c r="H163">
         <v>197</v>
       </c>
-      <c r="H163">
+      <c r="I163">
         <v>6</v>
       </c>
-      <c r="I163">
+      <c r="J163">
         <v>245</v>
       </c>
-      <c r="J163">
+      <c r="L163">
         <v>311</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2009</v>
       </c>
@@ -5632,20 +5644,20 @@
       <c r="E164">
         <v>4</v>
       </c>
-      <c r="F164">
+      <c r="G164">
         <v>26</v>
       </c>
-      <c r="G164">
+      <c r="H164">
         <v>28</v>
       </c>
-      <c r="I164">
+      <c r="J164">
         <v>61</v>
       </c>
-      <c r="J164">
+      <c r="L164">
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2009</v>
       </c>
@@ -5661,23 +5673,23 @@
       <c r="E165">
         <v>2823</v>
       </c>
-      <c r="F165">
+      <c r="G165">
         <v>609</v>
       </c>
-      <c r="G165">
+      <c r="H165">
         <v>1763</v>
       </c>
-      <c r="H165">
+      <c r="I165">
         <v>56</v>
       </c>
-      <c r="I165">
+      <c r="J165">
         <v>1412</v>
       </c>
-      <c r="J165">
+      <c r="L165">
         <v>1339</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2009</v>
       </c>
@@ -5693,23 +5705,23 @@
       <c r="E166">
         <v>8816</v>
       </c>
-      <c r="F166">
+      <c r="G166">
         <v>2244</v>
       </c>
-      <c r="G166">
+      <c r="H166">
         <v>3438</v>
       </c>
-      <c r="H166">
+      <c r="I166">
         <v>45</v>
       </c>
-      <c r="I166">
+      <c r="J166">
         <v>2916</v>
       </c>
-      <c r="J166">
+      <c r="L166">
         <v>4348</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2009</v>
       </c>
@@ -5725,23 +5737,23 @@
       <c r="E167">
         <v>332</v>
       </c>
-      <c r="F167">
+      <c r="G167">
         <v>86</v>
       </c>
-      <c r="G167">
+      <c r="H167">
         <v>780</v>
       </c>
-      <c r="H167">
+      <c r="I167">
         <v>12</v>
       </c>
-      <c r="I167">
+      <c r="J167">
         <v>311</v>
       </c>
-      <c r="J167">
+      <c r="L167">
         <v>372</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2009</v>
       </c>
@@ -5757,23 +5769,23 @@
       <c r="E168">
         <v>1965</v>
       </c>
-      <c r="F168">
+      <c r="G168">
         <v>865</v>
       </c>
-      <c r="G168">
+      <c r="H168">
         <v>1453</v>
       </c>
-      <c r="H168">
+      <c r="I168">
         <v>64</v>
       </c>
-      <c r="I168">
+      <c r="J168">
         <v>921</v>
       </c>
-      <c r="J168">
+      <c r="L168">
         <v>1222</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2009</v>
       </c>
@@ -5789,20 +5801,20 @@
       <c r="E169">
         <v>157</v>
       </c>
-      <c r="F169">
+      <c r="G169">
         <v>0</v>
       </c>
-      <c r="G169">
+      <c r="H169">
         <v>278</v>
       </c>
-      <c r="I169">
+      <c r="J169">
         <v>94</v>
       </c>
-      <c r="J169">
+      <c r="L169">
         <v>96</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2010</v>
       </c>
@@ -5812,8 +5824,35 @@
       <c r="C170" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D170">
+        <v>481</v>
+      </c>
+      <c r="E170">
+        <v>869</v>
+      </c>
+      <c r="F170">
+        <v>69</v>
+      </c>
+      <c r="G170">
+        <v>765</v>
+      </c>
+      <c r="H170">
+        <v>1181</v>
+      </c>
+      <c r="I170">
+        <v>34</v>
+      </c>
+      <c r="J170">
+        <v>1656</v>
+      </c>
+      <c r="K170">
+        <v>34</v>
+      </c>
+      <c r="L170">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2010</v>
       </c>
@@ -5823,8 +5862,26 @@
       <c r="C171" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D171">
+        <v>433</v>
+      </c>
+      <c r="E171">
+        <v>273</v>
+      </c>
+      <c r="G171">
+        <v>84</v>
+      </c>
+      <c r="H171">
+        <v>648</v>
+      </c>
+      <c r="J171">
+        <v>451</v>
+      </c>
+      <c r="L171">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2010</v>
       </c>
@@ -5835,7 +5892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2010</v>
       </c>
@@ -5845,8 +5902,35 @@
       <c r="C173" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D173">
+        <v>1926</v>
+      </c>
+      <c r="E173">
+        <v>3176</v>
+      </c>
+      <c r="F173">
+        <v>110</v>
+      </c>
+      <c r="G173">
+        <v>1621</v>
+      </c>
+      <c r="H173">
+        <v>2185</v>
+      </c>
+      <c r="I173">
+        <v>40</v>
+      </c>
+      <c r="J173">
+        <v>1587</v>
+      </c>
+      <c r="K173">
+        <v>9</v>
+      </c>
+      <c r="L173">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2010</v>
       </c>
@@ -5856,8 +5940,32 @@
       <c r="C174" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D174">
+        <v>505</v>
+      </c>
+      <c r="E174">
+        <v>450</v>
+      </c>
+      <c r="F174">
+        <v>194</v>
+      </c>
+      <c r="G174">
+        <v>346</v>
+      </c>
+      <c r="H174">
+        <v>975</v>
+      </c>
+      <c r="J174">
+        <v>770</v>
+      </c>
+      <c r="K174">
+        <v>25</v>
+      </c>
+      <c r="L174">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2010</v>
       </c>
@@ -5867,8 +5975,35 @@
       <c r="C175" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D175">
+        <v>7196</v>
+      </c>
+      <c r="E175">
+        <v>14820</v>
+      </c>
+      <c r="F175">
+        <v>1846</v>
+      </c>
+      <c r="G175">
+        <v>16379</v>
+      </c>
+      <c r="H175">
+        <v>12814</v>
+      </c>
+      <c r="I175">
+        <v>207</v>
+      </c>
+      <c r="J175">
+        <v>15245</v>
+      </c>
+      <c r="K175">
+        <v>929</v>
+      </c>
+      <c r="L175">
+        <v>23393</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2010</v>
       </c>
@@ -5878,8 +6013,35 @@
       <c r="C176" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176">
+        <v>1191</v>
+      </c>
+      <c r="E176">
+        <v>2331</v>
+      </c>
+      <c r="F176">
+        <v>2141</v>
+      </c>
+      <c r="G176">
+        <v>799</v>
+      </c>
+      <c r="H176">
+        <v>1400</v>
+      </c>
+      <c r="I176">
+        <v>25</v>
+      </c>
+      <c r="J176">
+        <v>1473</v>
+      </c>
+      <c r="K176">
+        <v>748</v>
+      </c>
+      <c r="L176">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2010</v>
       </c>
@@ -5889,8 +6051,32 @@
       <c r="C177" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177">
+        <v>955</v>
+      </c>
+      <c r="E177">
+        <v>734</v>
+      </c>
+      <c r="F177">
+        <v>93</v>
+      </c>
+      <c r="G177">
+        <v>1734</v>
+      </c>
+      <c r="H177">
+        <v>1315</v>
+      </c>
+      <c r="J177">
+        <v>917</v>
+      </c>
+      <c r="K177">
+        <v>40</v>
+      </c>
+      <c r="L177">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2010</v>
       </c>
@@ -5900,8 +6086,29 @@
       <c r="C178" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178">
+        <v>197</v>
+      </c>
+      <c r="E178">
+        <v>293</v>
+      </c>
+      <c r="G178">
+        <v>35</v>
+      </c>
+      <c r="H178">
+        <v>333</v>
+      </c>
+      <c r="I178">
+        <v>10</v>
+      </c>
+      <c r="J178">
+        <v>400</v>
+      </c>
+      <c r="L178">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2010</v>
       </c>
@@ -5911,8 +6118,29 @@
       <c r="C179" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179">
+        <v>1001</v>
+      </c>
+      <c r="E179">
+        <v>1660</v>
+      </c>
+      <c r="G179">
+        <v>1632</v>
+      </c>
+      <c r="H179">
+        <v>2470</v>
+      </c>
+      <c r="I179">
+        <v>25</v>
+      </c>
+      <c r="J179">
+        <v>1219</v>
+      </c>
+      <c r="L179">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2010</v>
       </c>
@@ -5922,8 +6150,35 @@
       <c r="C180" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180">
+        <v>3496</v>
+      </c>
+      <c r="E180">
+        <v>5459</v>
+      </c>
+      <c r="F180">
+        <v>370</v>
+      </c>
+      <c r="G180">
+        <v>1363</v>
+      </c>
+      <c r="H180">
+        <v>5922</v>
+      </c>
+      <c r="I180">
+        <v>172</v>
+      </c>
+      <c r="J180">
+        <v>8313</v>
+      </c>
+      <c r="K180">
+        <v>84</v>
+      </c>
+      <c r="L180">
+        <v>6013</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2010</v>
       </c>
@@ -5933,8 +6188,32 @@
       <c r="C181" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181">
+        <v>1432</v>
+      </c>
+      <c r="E181">
+        <v>2830</v>
+      </c>
+      <c r="F181">
+        <v>571</v>
+      </c>
+      <c r="G181">
+        <v>1960</v>
+      </c>
+      <c r="H181">
+        <v>3198</v>
+      </c>
+      <c r="J181">
+        <v>2505</v>
+      </c>
+      <c r="K181">
+        <v>93</v>
+      </c>
+      <c r="L181">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2010</v>
       </c>
@@ -5944,8 +6223,26 @@
       <c r="C182" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182">
+        <v>39</v>
+      </c>
+      <c r="E182">
+        <v>108</v>
+      </c>
+      <c r="G182">
+        <v>33</v>
+      </c>
+      <c r="H182">
+        <v>54</v>
+      </c>
+      <c r="J182">
+        <v>39</v>
+      </c>
+      <c r="L182">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2010</v>
       </c>
@@ -5955,8 +6252,35 @@
       <c r="C183" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183">
+        <v>825</v>
+      </c>
+      <c r="E183">
+        <v>2116</v>
+      </c>
+      <c r="F183">
+        <v>23</v>
+      </c>
+      <c r="G183">
+        <v>243</v>
+      </c>
+      <c r="H183">
+        <v>645</v>
+      </c>
+      <c r="I183">
+        <v>25</v>
+      </c>
+      <c r="J183">
+        <v>648</v>
+      </c>
+      <c r="K183">
+        <v>11</v>
+      </c>
+      <c r="L183">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2010</v>
       </c>
@@ -5966,8 +6290,32 @@
       <c r="C184" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184">
+        <v>408</v>
+      </c>
+      <c r="E184">
+        <v>570</v>
+      </c>
+      <c r="F184">
+        <v>84</v>
+      </c>
+      <c r="G184">
+        <v>180</v>
+      </c>
+      <c r="H184">
+        <v>573</v>
+      </c>
+      <c r="J184">
+        <v>354</v>
+      </c>
+      <c r="K184">
+        <v>22</v>
+      </c>
+      <c r="L184">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2010</v>
       </c>
@@ -5977,8 +6325,35 @@
       <c r="C185" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185">
+        <v>1843</v>
+      </c>
+      <c r="E185">
+        <v>5367</v>
+      </c>
+      <c r="F185">
+        <v>206</v>
+      </c>
+      <c r="G185">
+        <v>3685</v>
+      </c>
+      <c r="H185">
+        <v>3642</v>
+      </c>
+      <c r="I185">
+        <v>102</v>
+      </c>
+      <c r="J185">
+        <v>2601</v>
+      </c>
+      <c r="K185">
+        <v>47</v>
+      </c>
+      <c r="L185">
+        <v>7064</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2010</v>
       </c>
@@ -5988,8 +6363,35 @@
       <c r="C186" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186">
+        <v>1818</v>
+      </c>
+      <c r="E186">
+        <v>1907</v>
+      </c>
+      <c r="F186">
+        <v>858</v>
+      </c>
+      <c r="G186">
+        <v>1181</v>
+      </c>
+      <c r="H186">
+        <v>1942</v>
+      </c>
+      <c r="I186">
+        <v>25</v>
+      </c>
+      <c r="J186">
+        <v>1969</v>
+      </c>
+      <c r="K186">
+        <v>222</v>
+      </c>
+      <c r="L186">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2010</v>
       </c>
@@ -5999,8 +6401,32 @@
       <c r="C187" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187">
+        <v>691</v>
+      </c>
+      <c r="E187">
+        <v>1489</v>
+      </c>
+      <c r="F187">
+        <v>113</v>
+      </c>
+      <c r="G187">
+        <v>435</v>
+      </c>
+      <c r="H187">
+        <v>896</v>
+      </c>
+      <c r="J187">
+        <v>902</v>
+      </c>
+      <c r="K187">
+        <v>44</v>
+      </c>
+      <c r="L187">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2010</v>
       </c>
@@ -6010,8 +6436,35 @@
       <c r="C188" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188">
+        <v>783</v>
+      </c>
+      <c r="E188">
+        <v>692</v>
+      </c>
+      <c r="F188">
+        <v>13</v>
+      </c>
+      <c r="G188">
+        <v>341</v>
+      </c>
+      <c r="H188">
+        <v>839</v>
+      </c>
+      <c r="I188">
+        <v>20</v>
+      </c>
+      <c r="J188">
+        <v>453</v>
+      </c>
+      <c r="K188">
+        <v>6</v>
+      </c>
+      <c r="L188">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2010</v>
       </c>
@@ -6021,8 +6474,35 @@
       <c r="C189" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189">
+        <v>839</v>
+      </c>
+      <c r="E189">
+        <v>1704</v>
+      </c>
+      <c r="F189">
+        <v>271</v>
+      </c>
+      <c r="G189">
+        <v>1318</v>
+      </c>
+      <c r="H189">
+        <v>1822</v>
+      </c>
+      <c r="I189">
+        <v>12</v>
+      </c>
+      <c r="J189">
+        <v>1179</v>
+      </c>
+      <c r="K189">
+        <v>78</v>
+      </c>
+      <c r="L189">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2010</v>
       </c>
@@ -6032,8 +6512,35 @@
       <c r="C190" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190">
+        <v>784</v>
+      </c>
+      <c r="E190">
+        <v>1365</v>
+      </c>
+      <c r="F190">
+        <v>563</v>
+      </c>
+      <c r="G190">
+        <v>1000</v>
+      </c>
+      <c r="H190">
+        <v>1116</v>
+      </c>
+      <c r="I190">
+        <v>25</v>
+      </c>
+      <c r="J190">
+        <v>1858</v>
+      </c>
+      <c r="K190">
+        <v>112</v>
+      </c>
+      <c r="L190">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2010</v>
       </c>
@@ -6043,8 +6550,32 @@
       <c r="C191" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191">
+        <v>448</v>
+      </c>
+      <c r="E191">
+        <v>1136</v>
+      </c>
+      <c r="F191">
+        <v>151</v>
+      </c>
+      <c r="G191">
+        <v>754</v>
+      </c>
+      <c r="H191">
+        <v>599</v>
+      </c>
+      <c r="J191">
+        <v>541</v>
+      </c>
+      <c r="K191">
+        <v>146</v>
+      </c>
+      <c r="L191">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2010</v>
       </c>
@@ -6054,8 +6585,35 @@
       <c r="C192" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192">
+        <v>1218</v>
+      </c>
+      <c r="E192">
+        <v>1708</v>
+      </c>
+      <c r="F192">
+        <v>50</v>
+      </c>
+      <c r="G192">
+        <v>3113</v>
+      </c>
+      <c r="H192">
+        <v>1473</v>
+      </c>
+      <c r="I192">
+        <v>104</v>
+      </c>
+      <c r="J192">
+        <v>1397</v>
+      </c>
+      <c r="K192">
+        <v>19</v>
+      </c>
+      <c r="L192">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2010</v>
       </c>
@@ -6065,8 +6623,35 @@
       <c r="C193" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193">
+        <v>7859</v>
+      </c>
+      <c r="E193">
+        <v>2049</v>
+      </c>
+      <c r="F193">
+        <v>119</v>
+      </c>
+      <c r="G193">
+        <v>2298</v>
+      </c>
+      <c r="H193">
+        <v>2814</v>
+      </c>
+      <c r="I193">
+        <v>24</v>
+      </c>
+      <c r="J193">
+        <v>2763</v>
+      </c>
+      <c r="K193">
+        <v>51</v>
+      </c>
+      <c r="L193">
+        <v>6583</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2010</v>
       </c>
@@ -6076,8 +6661,35 @@
       <c r="C194" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194">
+        <v>2292</v>
+      </c>
+      <c r="E194">
+        <v>3899</v>
+      </c>
+      <c r="F194">
+        <v>543</v>
+      </c>
+      <c r="G194">
+        <v>7481</v>
+      </c>
+      <c r="H194">
+        <v>3276</v>
+      </c>
+      <c r="I194">
+        <v>43</v>
+      </c>
+      <c r="J194">
+        <v>2312</v>
+      </c>
+      <c r="K194">
+        <v>116</v>
+      </c>
+      <c r="L194">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2010</v>
       </c>
@@ -6087,8 +6699,35 @@
       <c r="C195" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195">
+        <v>1854</v>
+      </c>
+      <c r="E195">
+        <v>3046</v>
+      </c>
+      <c r="F195">
+        <v>399</v>
+      </c>
+      <c r="G195">
+        <v>4589</v>
+      </c>
+      <c r="H195">
+        <v>1535</v>
+      </c>
+      <c r="I195">
+        <v>10</v>
+      </c>
+      <c r="J195">
+        <v>880</v>
+      </c>
+      <c r="K195">
+        <v>162</v>
+      </c>
+      <c r="L195">
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2010</v>
       </c>
@@ -6098,8 +6737,32 @@
       <c r="C196" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196">
+        <v>276</v>
+      </c>
+      <c r="E196">
+        <v>263</v>
+      </c>
+      <c r="F196">
+        <v>79</v>
+      </c>
+      <c r="G196">
+        <v>70</v>
+      </c>
+      <c r="H196">
+        <v>460</v>
+      </c>
+      <c r="J196">
+        <v>377</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2010</v>
       </c>
@@ -6109,8 +6772,35 @@
       <c r="C197" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197">
+        <v>1832</v>
+      </c>
+      <c r="E197">
+        <v>2210</v>
+      </c>
+      <c r="F197">
+        <v>97</v>
+      </c>
+      <c r="G197">
+        <v>2438</v>
+      </c>
+      <c r="H197">
+        <v>1842</v>
+      </c>
+      <c r="I197">
+        <v>47</v>
+      </c>
+      <c r="J197">
+        <v>1509</v>
+      </c>
+      <c r="K197">
+        <v>18</v>
+      </c>
+      <c r="L197">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2010</v>
       </c>
@@ -6120,8 +6810,32 @@
       <c r="C198" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198">
+        <v>279</v>
+      </c>
+      <c r="E198">
+        <v>323</v>
+      </c>
+      <c r="F198">
+        <v>257</v>
+      </c>
+      <c r="G198">
+        <v>47</v>
+      </c>
+      <c r="H198">
+        <v>370</v>
+      </c>
+      <c r="J198">
+        <v>198</v>
+      </c>
+      <c r="K198">
+        <v>95</v>
+      </c>
+      <c r="L198">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2010</v>
       </c>
@@ -6131,8 +6845,32 @@
       <c r="C199" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199">
+        <v>713</v>
+      </c>
+      <c r="E199">
+        <v>1093</v>
+      </c>
+      <c r="F199">
+        <v>150</v>
+      </c>
+      <c r="G199">
+        <v>210</v>
+      </c>
+      <c r="H199">
+        <v>907</v>
+      </c>
+      <c r="J199">
+        <v>777</v>
+      </c>
+      <c r="K199">
+        <v>28</v>
+      </c>
+      <c r="L199">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2010</v>
       </c>
@@ -6142,8 +6880,29 @@
       <c r="C200" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200">
+        <v>564</v>
+      </c>
+      <c r="E200">
+        <v>832</v>
+      </c>
+      <c r="G200">
+        <v>356</v>
+      </c>
+      <c r="H200">
+        <v>915</v>
+      </c>
+      <c r="I200">
+        <v>25</v>
+      </c>
+      <c r="J200">
+        <v>1635</v>
+      </c>
+      <c r="L200">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2010</v>
       </c>
@@ -6153,8 +6912,35 @@
       <c r="C201" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201">
+        <v>314</v>
+      </c>
+      <c r="E201">
+        <v>437</v>
+      </c>
+      <c r="F201">
+        <v>132</v>
+      </c>
+      <c r="G201">
+        <v>411</v>
+      </c>
+      <c r="H201">
+        <v>356</v>
+      </c>
+      <c r="I201">
+        <v>9</v>
+      </c>
+      <c r="J201">
+        <v>258</v>
+      </c>
+      <c r="K201">
+        <v>52</v>
+      </c>
+      <c r="L201">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2010</v>
       </c>
@@ -6164,8 +6950,35 @@
       <c r="C202" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202">
+        <v>1941</v>
+      </c>
+      <c r="E202">
+        <v>1648</v>
+      </c>
+      <c r="F202">
+        <v>222</v>
+      </c>
+      <c r="G202">
+        <v>785</v>
+      </c>
+      <c r="H202">
+        <v>2314</v>
+      </c>
+      <c r="I202">
+        <v>20</v>
+      </c>
+      <c r="J202">
+        <v>922</v>
+      </c>
+      <c r="K202">
+        <v>82</v>
+      </c>
+      <c r="L202">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2010</v>
       </c>
@@ -6175,8 +6988,32 @@
       <c r="C203" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203">
+        <v>716</v>
+      </c>
+      <c r="E203">
+        <v>684</v>
+      </c>
+      <c r="F203">
+        <v>50</v>
+      </c>
+      <c r="G203">
+        <v>478</v>
+      </c>
+      <c r="H203">
+        <v>768</v>
+      </c>
+      <c r="J203">
+        <v>524</v>
+      </c>
+      <c r="K203">
+        <v>15</v>
+      </c>
+      <c r="L203">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2010</v>
       </c>
@@ -6186,8 +7023,35 @@
       <c r="C204" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204">
+        <v>36205</v>
+      </c>
+      <c r="E204">
+        <v>5389</v>
+      </c>
+      <c r="F204">
+        <v>488</v>
+      </c>
+      <c r="G204">
+        <v>12277</v>
+      </c>
+      <c r="H204">
+        <v>14578</v>
+      </c>
+      <c r="I204">
+        <v>140</v>
+      </c>
+      <c r="J204">
+        <v>7529</v>
+      </c>
+      <c r="K204">
+        <v>237</v>
+      </c>
+      <c r="L204">
+        <v>23237</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2010</v>
       </c>
@@ -6197,8 +7061,32 @@
       <c r="C205" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205">
+        <v>1832</v>
+      </c>
+      <c r="E205">
+        <v>1912</v>
+      </c>
+      <c r="F205">
+        <v>104</v>
+      </c>
+      <c r="G205">
+        <v>1529</v>
+      </c>
+      <c r="H205">
+        <v>3559</v>
+      </c>
+      <c r="J205">
+        <v>2665</v>
+      </c>
+      <c r="K205">
+        <v>46</v>
+      </c>
+      <c r="L205">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2010</v>
       </c>
@@ -6208,8 +7096,32 @@
       <c r="C206" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206">
+        <v>273</v>
+      </c>
+      <c r="E206">
+        <v>112</v>
+      </c>
+      <c r="F206">
+        <v>53</v>
+      </c>
+      <c r="G206">
+        <v>198</v>
+      </c>
+      <c r="H206">
+        <v>374</v>
+      </c>
+      <c r="J206">
+        <v>91</v>
+      </c>
+      <c r="K206">
+        <v>3</v>
+      </c>
+      <c r="L206">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2010</v>
       </c>
@@ -6220,7 +7132,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2010</v>
       </c>
@@ -6230,8 +7142,35 @@
       <c r="C208" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208">
+        <v>2173</v>
+      </c>
+      <c r="E208">
+        <v>2461</v>
+      </c>
+      <c r="F208">
+        <v>421</v>
+      </c>
+      <c r="G208">
+        <v>4216</v>
+      </c>
+      <c r="H208">
+        <v>4402</v>
+      </c>
+      <c r="I208">
+        <v>114</v>
+      </c>
+      <c r="J208">
+        <v>2174</v>
+      </c>
+      <c r="K208">
+        <v>287</v>
+      </c>
+      <c r="L208">
+        <v>7273</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2010</v>
       </c>
@@ -6241,8 +7180,35 @@
       <c r="C209" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209">
+        <v>812</v>
+      </c>
+      <c r="E209">
+        <v>512</v>
+      </c>
+      <c r="F209">
+        <v>71</v>
+      </c>
+      <c r="G209">
+        <v>184</v>
+      </c>
+      <c r="H209">
+        <v>1706</v>
+      </c>
+      <c r="I209">
+        <v>50</v>
+      </c>
+      <c r="J209">
+        <v>553</v>
+      </c>
+      <c r="K209">
+        <v>29</v>
+      </c>
+      <c r="L209">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2010</v>
       </c>
@@ -6252,8 +7218,35 @@
       <c r="C210" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210">
+        <v>1050</v>
+      </c>
+      <c r="E210">
+        <v>2534</v>
+      </c>
+      <c r="F210">
+        <v>269</v>
+      </c>
+      <c r="G210">
+        <v>1964</v>
+      </c>
+      <c r="H210">
+        <v>1976</v>
+      </c>
+      <c r="I210">
+        <v>43</v>
+      </c>
+      <c r="J210">
+        <v>2037</v>
+      </c>
+      <c r="K210">
+        <v>67</v>
+      </c>
+      <c r="L210">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2010</v>
       </c>
@@ -6263,8 +7256,35 @@
       <c r="C211" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211">
+        <v>3482</v>
+      </c>
+      <c r="E211">
+        <v>5576</v>
+      </c>
+      <c r="F211">
+        <v>577</v>
+      </c>
+      <c r="G211">
+        <v>4073</v>
+      </c>
+      <c r="H211">
+        <v>4407</v>
+      </c>
+      <c r="I211">
+        <v>173</v>
+      </c>
+      <c r="J211">
+        <v>2107</v>
+      </c>
+      <c r="K211">
+        <v>128</v>
+      </c>
+      <c r="L211">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2010</v>
       </c>
@@ -6274,8 +7294,35 @@
       <c r="C212" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212">
+        <v>196</v>
+      </c>
+      <c r="E212">
+        <v>285</v>
+      </c>
+      <c r="F212">
+        <v>19</v>
+      </c>
+      <c r="G212">
+        <v>370</v>
+      </c>
+      <c r="H212">
+        <v>417</v>
+      </c>
+      <c r="I212">
+        <v>32</v>
+      </c>
+      <c r="J212">
+        <v>1089</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2010</v>
       </c>
@@ -6285,8 +7332,35 @@
       <c r="C213" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213">
+        <v>319</v>
+      </c>
+      <c r="E213">
+        <v>255</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>644</v>
+      </c>
+      <c r="H213">
+        <v>452</v>
+      </c>
+      <c r="I213">
+        <v>17</v>
+      </c>
+      <c r="J213">
+        <v>172</v>
+      </c>
+      <c r="K213">
+        <v>4</v>
+      </c>
+      <c r="L213">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2010</v>
       </c>
@@ -6296,8 +7370,35 @@
       <c r="C214" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214">
+        <v>758</v>
+      </c>
+      <c r="E214">
+        <v>809</v>
+      </c>
+      <c r="F214">
+        <v>38</v>
+      </c>
+      <c r="G214">
+        <v>573</v>
+      </c>
+      <c r="H214">
+        <v>784</v>
+      </c>
+      <c r="I214">
+        <v>12</v>
+      </c>
+      <c r="J214">
+        <v>1145</v>
+      </c>
+      <c r="K214">
+        <v>16</v>
+      </c>
+      <c r="L214">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2010</v>
       </c>
@@ -6307,8 +7408,32 @@
       <c r="C215" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215">
+        <v>405</v>
+      </c>
+      <c r="E215">
+        <v>238</v>
+      </c>
+      <c r="F215">
+        <v>16</v>
+      </c>
+      <c r="G215">
+        <v>85</v>
+      </c>
+      <c r="H215">
+        <v>311</v>
+      </c>
+      <c r="J215">
+        <v>425</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2010</v>
       </c>
@@ -6318,8 +7443,35 @@
       <c r="C216" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216">
+        <v>841</v>
+      </c>
+      <c r="E216">
+        <v>1233</v>
+      </c>
+      <c r="F216">
+        <v>30</v>
+      </c>
+      <c r="G216">
+        <v>1002</v>
+      </c>
+      <c r="H216">
+        <v>2279</v>
+      </c>
+      <c r="I216">
+        <v>24</v>
+      </c>
+      <c r="J216">
+        <v>1825</v>
+      </c>
+      <c r="K216">
+        <v>250</v>
+      </c>
+      <c r="L216">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2010</v>
       </c>
@@ -6329,8 +7481,35 @@
       <c r="C217" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217">
+        <v>4881</v>
+      </c>
+      <c r="E217">
+        <v>5171</v>
+      </c>
+      <c r="F217">
+        <v>1629</v>
+      </c>
+      <c r="G217">
+        <v>2618</v>
+      </c>
+      <c r="H217">
+        <v>7860</v>
+      </c>
+      <c r="I217">
+        <v>182</v>
+      </c>
+      <c r="J217">
+        <v>4299</v>
+      </c>
+      <c r="K217">
+        <v>457</v>
+      </c>
+      <c r="L217">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2010</v>
       </c>
@@ -6340,8 +7519,35 @@
       <c r="C218" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218">
+        <v>659</v>
+      </c>
+      <c r="E218">
+        <v>1005</v>
+      </c>
+      <c r="F218">
+        <v>90</v>
+      </c>
+      <c r="G218">
+        <v>559</v>
+      </c>
+      <c r="H218">
+        <v>751</v>
+      </c>
+      <c r="I218">
+        <v>49</v>
+      </c>
+      <c r="J218">
+        <v>458</v>
+      </c>
+      <c r="K218">
+        <v>18</v>
+      </c>
+      <c r="L218">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2010</v>
       </c>
@@ -6351,8 +7557,35 @@
       <c r="C219" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219">
+        <v>214</v>
+      </c>
+      <c r="E219">
+        <v>175</v>
+      </c>
+      <c r="F219">
+        <v>100</v>
+      </c>
+      <c r="G219">
+        <v>44</v>
+      </c>
+      <c r="H219">
+        <v>181</v>
+      </c>
+      <c r="I219">
+        <v>6</v>
+      </c>
+      <c r="J219">
+        <v>210</v>
+      </c>
+      <c r="K219">
+        <v>21</v>
+      </c>
+      <c r="L219">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2010</v>
       </c>
@@ -6362,8 +7595,26 @@
       <c r="C220" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220">
+        <v>25</v>
+      </c>
+      <c r="E220">
+        <v>4</v>
+      </c>
+      <c r="G220">
+        <v>6</v>
+      </c>
+      <c r="H220">
+        <v>36</v>
+      </c>
+      <c r="J220">
+        <v>83</v>
+      </c>
+      <c r="L220">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2010</v>
       </c>
@@ -6373,8 +7624,35 @@
       <c r="C221" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221">
+        <v>1857</v>
+      </c>
+      <c r="E221">
+        <v>2657</v>
+      </c>
+      <c r="F221">
+        <v>138</v>
+      </c>
+      <c r="G221">
+        <v>586</v>
+      </c>
+      <c r="H221">
+        <v>1869</v>
+      </c>
+      <c r="I221">
+        <v>221</v>
+      </c>
+      <c r="J221">
+        <v>1345</v>
+      </c>
+      <c r="K221">
+        <v>40</v>
+      </c>
+      <c r="L221">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2010</v>
       </c>
@@ -6384,8 +7662,35 @@
       <c r="C222" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222">
+        <v>2533</v>
+      </c>
+      <c r="E222">
+        <v>9136</v>
+      </c>
+      <c r="F222">
+        <v>376</v>
+      </c>
+      <c r="G222">
+        <v>2500</v>
+      </c>
+      <c r="H222">
+        <v>3611</v>
+      </c>
+      <c r="I222">
+        <v>56</v>
+      </c>
+      <c r="J222">
+        <v>2735</v>
+      </c>
+      <c r="K222">
+        <v>58</v>
+      </c>
+      <c r="L222">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2010</v>
       </c>
@@ -6395,8 +7700,35 @@
       <c r="C223" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223">
+        <v>380</v>
+      </c>
+      <c r="E223">
+        <v>323</v>
+      </c>
+      <c r="F223">
+        <v>90</v>
+      </c>
+      <c r="G223">
+        <v>98</v>
+      </c>
+      <c r="H223">
+        <v>864</v>
+      </c>
+      <c r="I223">
+        <v>12</v>
+      </c>
+      <c r="J223">
+        <v>423</v>
+      </c>
+      <c r="K223">
+        <v>7</v>
+      </c>
+      <c r="L223">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2010</v>
       </c>
@@ -6406,8 +7738,35 @@
       <c r="C224" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224">
+        <v>1647</v>
+      </c>
+      <c r="E224">
+        <v>2013</v>
+      </c>
+      <c r="F224">
+        <v>505</v>
+      </c>
+      <c r="G224">
+        <v>781</v>
+      </c>
+      <c r="H224">
+        <v>1345</v>
+      </c>
+      <c r="I224">
+        <v>64</v>
+      </c>
+      <c r="J224">
+        <v>939</v>
+      </c>
+      <c r="K224">
+        <v>85</v>
+      </c>
+      <c r="L224">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2010</v>
       </c>
@@ -6417,8 +7776,32 @@
       <c r="C225" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225">
+        <v>259</v>
+      </c>
+      <c r="E225">
+        <v>171</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>299</v>
+      </c>
+      <c r="J225">
+        <v>175</v>
+      </c>
+      <c r="K225">
+        <v>7</v>
+      </c>
+      <c r="L225">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2011</v>
       </c>
@@ -6428,8 +7811,35 @@
       <c r="C226" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226">
+        <v>652</v>
+      </c>
+      <c r="E226">
+        <v>910</v>
+      </c>
+      <c r="F226">
+        <v>72</v>
+      </c>
+      <c r="G226">
+        <v>871</v>
+      </c>
+      <c r="H226">
+        <v>1178</v>
+      </c>
+      <c r="I226">
+        <v>34</v>
+      </c>
+      <c r="J226">
+        <v>1723</v>
+      </c>
+      <c r="K226">
+        <v>21</v>
+      </c>
+      <c r="L226">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2011</v>
       </c>
@@ -6439,8 +7849,32 @@
       <c r="C227" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227">
+        <v>519</v>
+      </c>
+      <c r="E227">
+        <v>299</v>
+      </c>
+      <c r="F227">
+        <v>5</v>
+      </c>
+      <c r="G227">
+        <v>129</v>
+      </c>
+      <c r="H227">
+        <v>637</v>
+      </c>
+      <c r="J227">
+        <v>432</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2011</v>
       </c>
@@ -6451,7 +7885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2011</v>
       </c>
@@ -6461,8 +7895,35 @@
       <c r="C229" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229">
+        <v>1821</v>
+      </c>
+      <c r="E229">
+        <v>2948</v>
+      </c>
+      <c r="F229">
+        <v>2992</v>
+      </c>
+      <c r="G229">
+        <v>1582</v>
+      </c>
+      <c r="H229">
+        <v>2270</v>
+      </c>
+      <c r="I229">
+        <v>40</v>
+      </c>
+      <c r="J229">
+        <v>1669</v>
+      </c>
+      <c r="K229">
+        <v>561</v>
+      </c>
+      <c r="L229">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2011</v>
       </c>
@@ -6472,8 +7933,32 @@
       <c r="C230" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230">
+        <v>644</v>
+      </c>
+      <c r="E230">
+        <v>408</v>
+      </c>
+      <c r="F230">
+        <v>189</v>
+      </c>
+      <c r="G230">
+        <v>364</v>
+      </c>
+      <c r="H230">
+        <v>946</v>
+      </c>
+      <c r="J230">
+        <v>712</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2011</v>
       </c>
@@ -6483,8 +7968,35 @@
       <c r="C231" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231">
+        <v>7959</v>
+      </c>
+      <c r="E231">
+        <v>15084</v>
+      </c>
+      <c r="F231">
+        <v>3622</v>
+      </c>
+      <c r="G231">
+        <v>17893</v>
+      </c>
+      <c r="H231">
+        <v>11999</v>
+      </c>
+      <c r="I231">
+        <v>198</v>
+      </c>
+      <c r="J231">
+        <v>14417</v>
+      </c>
+      <c r="K231">
+        <v>1035</v>
+      </c>
+      <c r="L231">
+        <v>24637</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2011</v>
       </c>
@@ -6494,8 +8006,35 @@
       <c r="C232" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232">
+        <v>1230</v>
+      </c>
+      <c r="E232">
+        <v>2245</v>
+      </c>
+      <c r="F232">
+        <v>511</v>
+      </c>
+      <c r="G232">
+        <v>838</v>
+      </c>
+      <c r="H232">
+        <v>1389</v>
+      </c>
+      <c r="I232">
+        <v>25</v>
+      </c>
+      <c r="J232">
+        <v>1472</v>
+      </c>
+      <c r="K232">
+        <v>374</v>
+      </c>
+      <c r="L232">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2011</v>
       </c>
@@ -6505,8 +8044,32 @@
       <c r="C233" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233">
+        <v>945</v>
+      </c>
+      <c r="E233">
+        <v>651</v>
+      </c>
+      <c r="F233">
+        <v>120</v>
+      </c>
+      <c r="G233">
+        <v>1976</v>
+      </c>
+      <c r="H233">
+        <v>1388</v>
+      </c>
+      <c r="J233">
+        <v>922</v>
+      </c>
+      <c r="K233">
+        <v>118</v>
+      </c>
+      <c r="L233">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2011</v>
       </c>
@@ -6516,8 +8079,29 @@
       <c r="C234" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234">
+        <v>201</v>
+      </c>
+      <c r="E234">
+        <v>340</v>
+      </c>
+      <c r="G234">
+        <v>37</v>
+      </c>
+      <c r="H234">
+        <v>314</v>
+      </c>
+      <c r="I234">
+        <v>10</v>
+      </c>
+      <c r="J234">
+        <v>351</v>
+      </c>
+      <c r="L234">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2011</v>
       </c>
@@ -6527,8 +8111,32 @@
       <c r="C235" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235">
+        <v>1082</v>
+      </c>
+      <c r="E235">
+        <v>1951</v>
+      </c>
+      <c r="F235">
+        <v>366</v>
+      </c>
+      <c r="G235">
+        <v>2222</v>
+      </c>
+      <c r="H235">
+        <v>2345</v>
+      </c>
+      <c r="J235">
+        <v>1101</v>
+      </c>
+      <c r="K235">
+        <v>294</v>
+      </c>
+      <c r="L235">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2011</v>
       </c>
@@ -6538,8 +8146,35 @@
       <c r="C236" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236">
+        <v>3713</v>
+      </c>
+      <c r="E236">
+        <v>5977</v>
+      </c>
+      <c r="F236">
+        <v>1276</v>
+      </c>
+      <c r="G236">
+        <v>4445</v>
+      </c>
+      <c r="H236">
+        <v>6079</v>
+      </c>
+      <c r="I236">
+        <v>178</v>
+      </c>
+      <c r="J236">
+        <v>8045</v>
+      </c>
+      <c r="K236">
+        <v>246</v>
+      </c>
+      <c r="L236">
+        <v>7323</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2011</v>
       </c>
@@ -6549,8 +8184,32 @@
       <c r="C237" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237">
+        <v>1566</v>
+      </c>
+      <c r="E237">
+        <v>3261</v>
+      </c>
+      <c r="F237">
+        <v>365</v>
+      </c>
+      <c r="G237">
+        <v>2767</v>
+      </c>
+      <c r="H237">
+        <v>3571</v>
+      </c>
+      <c r="J237">
+        <v>2769</v>
+      </c>
+      <c r="K237">
+        <v>112</v>
+      </c>
+      <c r="L237">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2011</v>
       </c>
@@ -6560,8 +8219,32 @@
       <c r="C238" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238">
+        <v>75</v>
+      </c>
+      <c r="E238">
+        <v>118</v>
+      </c>
+      <c r="F238">
+        <v>38</v>
+      </c>
+      <c r="G238">
+        <v>37</v>
+      </c>
+      <c r="H238">
+        <v>34</v>
+      </c>
+      <c r="J238">
+        <v>37</v>
+      </c>
+      <c r="K238">
+        <v>6</v>
+      </c>
+      <c r="L238">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2011</v>
       </c>
@@ -6571,8 +8254,35 @@
       <c r="C239" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239">
+        <v>893</v>
+      </c>
+      <c r="E239">
+        <v>2128</v>
+      </c>
+      <c r="F239">
+        <v>17</v>
+      </c>
+      <c r="G239">
+        <v>257</v>
+      </c>
+      <c r="H239">
+        <v>629</v>
+      </c>
+      <c r="I239">
+        <v>25</v>
+      </c>
+      <c r="J239">
+        <v>575</v>
+      </c>
+      <c r="K239">
+        <v>7</v>
+      </c>
+      <c r="L239">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2011</v>
       </c>
@@ -6582,8 +8292,32 @@
       <c r="C240" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240">
+        <v>423</v>
+      </c>
+      <c r="E240">
+        <v>601</v>
+      </c>
+      <c r="F240">
+        <v>101</v>
+      </c>
+      <c r="G240">
+        <v>246</v>
+      </c>
+      <c r="H240">
+        <v>535</v>
+      </c>
+      <c r="J240">
+        <v>336</v>
+      </c>
+      <c r="K240">
+        <v>17</v>
+      </c>
+      <c r="L240">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2011</v>
       </c>
@@ -6593,8 +8327,35 @@
       <c r="C241" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241">
+        <v>1604</v>
+      </c>
+      <c r="E241">
+        <v>4997</v>
+      </c>
+      <c r="F241">
+        <v>783</v>
+      </c>
+      <c r="G241">
+        <v>3936</v>
+      </c>
+      <c r="H241">
+        <v>3991</v>
+      </c>
+      <c r="I241">
+        <v>102</v>
+      </c>
+      <c r="J241">
+        <v>2351</v>
+      </c>
+      <c r="K241">
+        <v>281</v>
+      </c>
+      <c r="L241">
+        <v>6901</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2011</v>
       </c>
@@ -6604,8 +8365,35 @@
       <c r="C242" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242">
+        <v>1971</v>
+      </c>
+      <c r="E242">
+        <v>1912</v>
+      </c>
+      <c r="F242">
+        <v>1999</v>
+      </c>
+      <c r="G242">
+        <v>771</v>
+      </c>
+      <c r="H242">
+        <v>1867</v>
+      </c>
+      <c r="I242">
+        <v>25</v>
+      </c>
+      <c r="J242">
+        <v>1470</v>
+      </c>
+      <c r="K242">
+        <v>532</v>
+      </c>
+      <c r="L242">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2011</v>
       </c>
@@ -6615,8 +8403,32 @@
       <c r="C243" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243">
+        <v>748</v>
+      </c>
+      <c r="E243">
+        <v>1504</v>
+      </c>
+      <c r="F243">
+        <v>190</v>
+      </c>
+      <c r="G243">
+        <v>430</v>
+      </c>
+      <c r="H243">
+        <v>830</v>
+      </c>
+      <c r="J243">
+        <v>900</v>
+      </c>
+      <c r="K243">
+        <v>13</v>
+      </c>
+      <c r="L243">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2011</v>
       </c>
@@ -6626,8 +8438,35 @@
       <c r="C244" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244">
+        <v>822</v>
+      </c>
+      <c r="E244">
+        <v>773</v>
+      </c>
+      <c r="F244">
+        <v>80</v>
+      </c>
+      <c r="G244">
+        <v>249</v>
+      </c>
+      <c r="H244">
+        <v>888</v>
+      </c>
+      <c r="I244">
+        <v>20</v>
+      </c>
+      <c r="J244">
+        <v>439</v>
+      </c>
+      <c r="K244">
+        <v>22</v>
+      </c>
+      <c r="L244">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2011</v>
       </c>
@@ -6637,8 +8476,35 @@
       <c r="C245" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245">
+        <v>973</v>
+      </c>
+      <c r="E245">
+        <v>1386</v>
+      </c>
+      <c r="F245">
+        <v>112</v>
+      </c>
+      <c r="G245">
+        <v>1543</v>
+      </c>
+      <c r="H245">
+        <v>1600</v>
+      </c>
+      <c r="I245">
+        <v>12</v>
+      </c>
+      <c r="J245">
+        <v>1418</v>
+      </c>
+      <c r="K245">
+        <v>35</v>
+      </c>
+      <c r="L245">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2011</v>
       </c>
@@ -6648,8 +8514,35 @@
       <c r="C246" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246">
+        <v>779</v>
+      </c>
+      <c r="E246">
+        <v>1285</v>
+      </c>
+      <c r="F246">
+        <v>433</v>
+      </c>
+      <c r="G246">
+        <v>955</v>
+      </c>
+      <c r="H246">
+        <v>1086</v>
+      </c>
+      <c r="I246">
+        <v>37</v>
+      </c>
+      <c r="J246">
+        <v>1886</v>
+      </c>
+      <c r="K246">
+        <v>189</v>
+      </c>
+      <c r="L246">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2011</v>
       </c>
@@ -6659,8 +8552,35 @@
       <c r="C247" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247">
+        <v>488</v>
+      </c>
+      <c r="E247">
+        <v>1120</v>
+      </c>
+      <c r="F247">
+        <v>255</v>
+      </c>
+      <c r="G247">
+        <v>764</v>
+      </c>
+      <c r="H247">
+        <v>592</v>
+      </c>
+      <c r="I247">
+        <v>15</v>
+      </c>
+      <c r="J247">
+        <v>586</v>
+      </c>
+      <c r="K247">
+        <v>237</v>
+      </c>
+      <c r="L247">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2011</v>
       </c>
@@ -6670,8 +8590,35 @@
       <c r="C248" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248">
+        <v>1229</v>
+      </c>
+      <c r="E248">
+        <v>1722</v>
+      </c>
+      <c r="F248">
+        <v>270</v>
+      </c>
+      <c r="G248">
+        <v>3259</v>
+      </c>
+      <c r="H248">
+        <v>1637</v>
+      </c>
+      <c r="I248">
+        <v>104</v>
+      </c>
+      <c r="J248">
+        <v>1592</v>
+      </c>
+      <c r="K248">
+        <v>25</v>
+      </c>
+      <c r="L248">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2011</v>
       </c>
@@ -6681,8 +8628,35 @@
       <c r="C249" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249">
+        <v>7127</v>
+      </c>
+      <c r="E249">
+        <v>1969</v>
+      </c>
+      <c r="F249">
+        <v>699</v>
+      </c>
+      <c r="G249">
+        <v>2750</v>
+      </c>
+      <c r="H249">
+        <v>2744</v>
+      </c>
+      <c r="I249">
+        <v>38</v>
+      </c>
+      <c r="J249">
+        <v>2689</v>
+      </c>
+      <c r="K249">
+        <v>360</v>
+      </c>
+      <c r="L249">
+        <v>7411</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2011</v>
       </c>
@@ -6692,8 +8666,35 @@
       <c r="C250" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250">
+        <v>2353</v>
+      </c>
+      <c r="E250">
+        <v>3885</v>
+      </c>
+      <c r="F250">
+        <v>1729</v>
+      </c>
+      <c r="G250">
+        <v>8561</v>
+      </c>
+      <c r="H250">
+        <v>3358</v>
+      </c>
+      <c r="I250">
+        <v>43</v>
+      </c>
+      <c r="J250">
+        <v>2360</v>
+      </c>
+      <c r="K250">
+        <v>461</v>
+      </c>
+      <c r="L250">
+        <v>5991</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2011</v>
       </c>
@@ -6703,8 +8704,35 @@
       <c r="C251" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251">
+        <v>2132</v>
+      </c>
+      <c r="E251">
+        <v>2628</v>
+      </c>
+      <c r="F251">
+        <v>1270</v>
+      </c>
+      <c r="G251">
+        <v>4921</v>
+      </c>
+      <c r="H251">
+        <v>1466</v>
+      </c>
+      <c r="I251">
+        <v>21</v>
+      </c>
+      <c r="J251">
+        <v>726</v>
+      </c>
+      <c r="K251">
+        <v>505</v>
+      </c>
+      <c r="L251">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2011</v>
       </c>
@@ -6714,8 +8742,35 @@
       <c r="C252" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252">
+        <v>388</v>
+      </c>
+      <c r="E252">
+        <v>306</v>
+      </c>
+      <c r="F252">
+        <v>379</v>
+      </c>
+      <c r="G252">
+        <v>54</v>
+      </c>
+      <c r="H252">
+        <v>301</v>
+      </c>
+      <c r="I252">
+        <v>3</v>
+      </c>
+      <c r="J252">
+        <v>375</v>
+      </c>
+      <c r="K252">
+        <v>65</v>
+      </c>
+      <c r="L252">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2011</v>
       </c>
@@ -6725,8 +8780,35 @@
       <c r="C253" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253">
+        <v>2059</v>
+      </c>
+      <c r="E253">
+        <v>2113</v>
+      </c>
+      <c r="F253">
+        <v>400</v>
+      </c>
+      <c r="G253">
+        <v>2434</v>
+      </c>
+      <c r="H253">
+        <v>2081</v>
+      </c>
+      <c r="I253">
+        <v>51</v>
+      </c>
+      <c r="J253">
+        <v>1832</v>
+      </c>
+      <c r="K253">
+        <v>134</v>
+      </c>
+      <c r="L253">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>2011</v>
       </c>
@@ -6736,8 +8818,32 @@
       <c r="C254" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254">
+        <v>324</v>
+      </c>
+      <c r="E254">
+        <v>322</v>
+      </c>
+      <c r="F254">
+        <v>379</v>
+      </c>
+      <c r="G254">
+        <v>61</v>
+      </c>
+      <c r="H254">
+        <v>375</v>
+      </c>
+      <c r="J254">
+        <v>186</v>
+      </c>
+      <c r="K254">
+        <v>180</v>
+      </c>
+      <c r="L254">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>2011</v>
       </c>
@@ -6747,8 +8853,32 @@
       <c r="C255" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255">
+        <v>862</v>
+      </c>
+      <c r="E255">
+        <v>1125</v>
+      </c>
+      <c r="F255">
+        <v>203</v>
+      </c>
+      <c r="G255">
+        <v>329</v>
+      </c>
+      <c r="H255">
+        <v>1011</v>
+      </c>
+      <c r="J255">
+        <v>809</v>
+      </c>
+      <c r="K255">
+        <v>84</v>
+      </c>
+      <c r="L255">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>2011</v>
       </c>
@@ -6758,8 +8888,35 @@
       <c r="C256" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256">
+        <v>615</v>
+      </c>
+      <c r="E256">
+        <v>1024</v>
+      </c>
+      <c r="F256">
+        <v>5</v>
+      </c>
+      <c r="G256">
+        <v>658</v>
+      </c>
+      <c r="H256">
+        <v>868</v>
+      </c>
+      <c r="I256">
+        <v>25</v>
+      </c>
+      <c r="J256">
+        <v>2243</v>
+      </c>
+      <c r="K256">
+        <v>4</v>
+      </c>
+      <c r="L256">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2011</v>
       </c>
@@ -6769,8 +8926,35 @@
       <c r="C257" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D257">
+        <v>287</v>
+      </c>
+      <c r="E257">
+        <v>457</v>
+      </c>
+      <c r="F257">
+        <v>227</v>
+      </c>
+      <c r="G257">
+        <v>487</v>
+      </c>
+      <c r="H257">
+        <v>371</v>
+      </c>
+      <c r="I257">
+        <v>9</v>
+      </c>
+      <c r="J257">
+        <v>236</v>
+      </c>
+      <c r="K257">
+        <v>60</v>
+      </c>
+      <c r="L257">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2011</v>
       </c>
@@ -6780,8 +8964,35 @@
       <c r="C258" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D258">
+        <v>2021</v>
+      </c>
+      <c r="E258">
+        <v>1960</v>
+      </c>
+      <c r="F258">
+        <v>706</v>
+      </c>
+      <c r="G258">
+        <v>1227</v>
+      </c>
+      <c r="H258">
+        <v>2681</v>
+      </c>
+      <c r="I258">
+        <v>28</v>
+      </c>
+      <c r="J258">
+        <v>886</v>
+      </c>
+      <c r="K258">
+        <v>442</v>
+      </c>
+      <c r="L258">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2011</v>
       </c>
@@ -6791,8 +9002,32 @@
       <c r="C259" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D259">
+        <v>826</v>
+      </c>
+      <c r="E259">
+        <v>729</v>
+      </c>
+      <c r="F259">
+        <v>181</v>
+      </c>
+      <c r="G259">
+        <v>481</v>
+      </c>
+      <c r="H259">
+        <v>803</v>
+      </c>
+      <c r="J259">
+        <v>439</v>
+      </c>
+      <c r="K259">
+        <v>69</v>
+      </c>
+      <c r="L259">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2011</v>
       </c>
@@ -6802,8 +9037,35 @@
       <c r="C260" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D260">
+        <v>35028</v>
+      </c>
+      <c r="E260">
+        <v>5173</v>
+      </c>
+      <c r="F260">
+        <v>1195</v>
+      </c>
+      <c r="G260">
+        <v>13421</v>
+      </c>
+      <c r="H260">
+        <v>16625</v>
+      </c>
+      <c r="I260">
+        <v>143</v>
+      </c>
+      <c r="J260">
+        <v>7114</v>
+      </c>
+      <c r="K260">
+        <v>368</v>
+      </c>
+      <c r="L260">
+        <v>26161</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>2011</v>
       </c>
@@ -6813,8 +9075,32 @@
       <c r="C261" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D261">
+        <v>1960</v>
+      </c>
+      <c r="E261">
+        <v>1854</v>
+      </c>
+      <c r="F261">
+        <v>1095</v>
+      </c>
+      <c r="G261">
+        <v>2004</v>
+      </c>
+      <c r="H261">
+        <v>3658</v>
+      </c>
+      <c r="J261">
+        <v>2805</v>
+      </c>
+      <c r="K261">
+        <v>274</v>
+      </c>
+      <c r="L261">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>2011</v>
       </c>
@@ -6824,8 +9110,32 @@
       <c r="C262" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D262">
+        <v>234</v>
+      </c>
+      <c r="E262">
+        <v>90</v>
+      </c>
+      <c r="F262">
+        <v>62</v>
+      </c>
+      <c r="G262">
+        <v>141</v>
+      </c>
+      <c r="H262">
+        <v>351</v>
+      </c>
+      <c r="J262">
+        <v>64</v>
+      </c>
+      <c r="K262">
+        <v>18</v>
+      </c>
+      <c r="L262">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>2011</v>
       </c>
@@ -6836,7 +9146,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>2011</v>
       </c>
@@ -6846,8 +9156,35 @@
       <c r="C264" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D264">
+        <v>2372</v>
+      </c>
+      <c r="E264">
+        <v>3099</v>
+      </c>
+      <c r="F264">
+        <v>1212</v>
+      </c>
+      <c r="G264">
+        <v>4163</v>
+      </c>
+      <c r="H264">
+        <v>3750</v>
+      </c>
+      <c r="I264">
+        <v>96</v>
+      </c>
+      <c r="J264">
+        <v>2376</v>
+      </c>
+      <c r="K264">
+        <v>943</v>
+      </c>
+      <c r="L264">
+        <v>7671</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2011</v>
       </c>
@@ -6857,8 +9194,35 @@
       <c r="C265" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D265">
+        <v>978</v>
+      </c>
+      <c r="E265">
+        <v>562</v>
+      </c>
+      <c r="F265">
+        <v>379</v>
+      </c>
+      <c r="G265">
+        <v>185</v>
+      </c>
+      <c r="H265">
+        <v>1553</v>
+      </c>
+      <c r="I265">
+        <v>59</v>
+      </c>
+      <c r="J265">
+        <v>480</v>
+      </c>
+      <c r="K265">
+        <v>27</v>
+      </c>
+      <c r="L265">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2011</v>
       </c>
@@ -6868,8 +9232,35 @@
       <c r="C266" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D266">
+        <v>1044</v>
+      </c>
+      <c r="E266">
+        <v>2789</v>
+      </c>
+      <c r="F266">
+        <v>374</v>
+      </c>
+      <c r="G266">
+        <v>1546</v>
+      </c>
+      <c r="H266">
+        <v>1680</v>
+      </c>
+      <c r="I266">
+        <v>43</v>
+      </c>
+      <c r="J266">
+        <v>1821</v>
+      </c>
+      <c r="K266">
+        <v>73</v>
+      </c>
+      <c r="L266">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2011</v>
       </c>
@@ -6879,8 +9270,35 @@
       <c r="C267" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D267">
+        <v>3688</v>
+      </c>
+      <c r="E267">
+        <v>5468</v>
+      </c>
+      <c r="F267">
+        <v>3569</v>
+      </c>
+      <c r="G267">
+        <v>5031</v>
+      </c>
+      <c r="H267">
+        <v>4460</v>
+      </c>
+      <c r="I267">
+        <v>173</v>
+      </c>
+      <c r="J267">
+        <v>2574</v>
+      </c>
+      <c r="K267">
+        <v>830</v>
+      </c>
+      <c r="L267">
+        <v>4864</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2011</v>
       </c>
@@ -6890,8 +9308,35 @@
       <c r="C268" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D268">
+        <v>154</v>
+      </c>
+      <c r="E268">
+        <v>360</v>
+      </c>
+      <c r="F268">
+        <v>941</v>
+      </c>
+      <c r="G268">
+        <v>326</v>
+      </c>
+      <c r="H268">
+        <v>464</v>
+      </c>
+      <c r="I268">
+        <v>77</v>
+      </c>
+      <c r="J268">
+        <v>998</v>
+      </c>
+      <c r="K268">
+        <v>245</v>
+      </c>
+      <c r="L268">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>2011</v>
       </c>
@@ -6901,8 +9346,35 @@
       <c r="C269" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D269">
+        <v>345</v>
+      </c>
+      <c r="E269">
+        <v>317</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>652</v>
+      </c>
+      <c r="H269">
+        <v>422</v>
+      </c>
+      <c r="I269">
+        <v>18</v>
+      </c>
+      <c r="J269">
+        <v>198</v>
+      </c>
+      <c r="K269">
+        <v>48</v>
+      </c>
+      <c r="L269">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>2011</v>
       </c>
@@ -6912,8 +9384,35 @@
       <c r="C270" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D270">
+        <v>713</v>
+      </c>
+      <c r="E270">
+        <v>867</v>
+      </c>
+      <c r="F270">
+        <v>129</v>
+      </c>
+      <c r="G270">
+        <v>632</v>
+      </c>
+      <c r="H270">
+        <v>974</v>
+      </c>
+      <c r="I270">
+        <v>12</v>
+      </c>
+      <c r="J270">
+        <v>1225</v>
+      </c>
+      <c r="K270">
+        <v>83</v>
+      </c>
+      <c r="L270">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>2011</v>
       </c>
@@ -6923,8 +9422,32 @@
       <c r="C271" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D271">
+        <v>451</v>
+      </c>
+      <c r="E271">
+        <v>262</v>
+      </c>
+      <c r="F271">
+        <v>192</v>
+      </c>
+      <c r="G271">
+        <v>133</v>
+      </c>
+      <c r="H271">
+        <v>267</v>
+      </c>
+      <c r="J271">
+        <v>339</v>
+      </c>
+      <c r="K271">
+        <v>0</v>
+      </c>
+      <c r="L271">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>2011</v>
       </c>
@@ -6934,8 +9457,35 @@
       <c r="C272" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D272">
+        <v>1050</v>
+      </c>
+      <c r="E272">
+        <v>1355</v>
+      </c>
+      <c r="F272">
+        <v>319</v>
+      </c>
+      <c r="G272">
+        <v>1402</v>
+      </c>
+      <c r="H272">
+        <v>2109</v>
+      </c>
+      <c r="I272">
+        <v>24</v>
+      </c>
+      <c r="J272">
+        <v>2208</v>
+      </c>
+      <c r="K272">
+        <v>76</v>
+      </c>
+      <c r="L272">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2011</v>
       </c>
@@ -6945,8 +9495,35 @@
       <c r="C273" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D273">
+        <v>5217</v>
+      </c>
+      <c r="E273">
+        <v>5657</v>
+      </c>
+      <c r="F273">
+        <v>1032</v>
+      </c>
+      <c r="G273">
+        <v>3654</v>
+      </c>
+      <c r="H273">
+        <v>8012</v>
+      </c>
+      <c r="I273">
+        <v>186</v>
+      </c>
+      <c r="J273">
+        <v>5245</v>
+      </c>
+      <c r="K273">
+        <v>263</v>
+      </c>
+      <c r="L273">
+        <v>5401</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2011</v>
       </c>
@@ -6956,8 +9533,35 @@
       <c r="C274" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D274">
+        <v>703</v>
+      </c>
+      <c r="E274">
+        <v>905</v>
+      </c>
+      <c r="F274">
+        <v>879</v>
+      </c>
+      <c r="G274">
+        <v>599</v>
+      </c>
+      <c r="H274">
+        <v>798</v>
+      </c>
+      <c r="I274">
+        <v>49</v>
+      </c>
+      <c r="J274">
+        <v>499</v>
+      </c>
+      <c r="K274">
+        <v>22</v>
+      </c>
+      <c r="L274">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2011</v>
       </c>
@@ -6967,8 +9571,29 @@
       <c r="C275" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D275">
+        <v>257</v>
+      </c>
+      <c r="E275">
+        <v>212</v>
+      </c>
+      <c r="G275">
+        <v>104</v>
+      </c>
+      <c r="H275">
+        <v>197</v>
+      </c>
+      <c r="I275">
+        <v>6</v>
+      </c>
+      <c r="J275">
+        <v>133</v>
+      </c>
+      <c r="L275">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2011</v>
       </c>
@@ -6978,8 +9603,26 @@
       <c r="C276" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D276">
+        <v>44</v>
+      </c>
+      <c r="E276">
+        <v>28</v>
+      </c>
+      <c r="G276">
+        <v>26</v>
+      </c>
+      <c r="H276">
+        <v>27</v>
+      </c>
+      <c r="J276">
+        <v>96</v>
+      </c>
+      <c r="L276">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>2011</v>
       </c>
@@ -6989,8 +9632,35 @@
       <c r="C277" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D277">
+        <v>1893</v>
+      </c>
+      <c r="E277">
+        <v>2618</v>
+      </c>
+      <c r="F277">
+        <v>169</v>
+      </c>
+      <c r="G277">
+        <v>891</v>
+      </c>
+      <c r="H277">
+        <v>1841</v>
+      </c>
+      <c r="I277">
+        <v>57</v>
+      </c>
+      <c r="J277">
+        <v>1281</v>
+      </c>
+      <c r="K277">
+        <v>88</v>
+      </c>
+      <c r="L277">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>2011</v>
       </c>
@@ -7000,8 +9670,35 @@
       <c r="C278" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D278">
+        <v>2812</v>
+      </c>
+      <c r="E278">
+        <v>7878</v>
+      </c>
+      <c r="F278">
+        <v>667</v>
+      </c>
+      <c r="G278">
+        <v>2475</v>
+      </c>
+      <c r="H278">
+        <v>3457</v>
+      </c>
+      <c r="I278">
+        <v>55</v>
+      </c>
+      <c r="J278">
+        <v>2467</v>
+      </c>
+      <c r="K278">
+        <v>192</v>
+      </c>
+      <c r="L278">
+        <v>6124</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>2011</v>
       </c>
@@ -7011,8 +9708,35 @@
       <c r="C279" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D279">
+        <v>379</v>
+      </c>
+      <c r="E279">
+        <v>361</v>
+      </c>
+      <c r="F279">
+        <v>910</v>
+      </c>
+      <c r="G279">
+        <v>168</v>
+      </c>
+      <c r="H279">
+        <v>825</v>
+      </c>
+      <c r="I279">
+        <v>11</v>
+      </c>
+      <c r="J279">
+        <v>302</v>
+      </c>
+      <c r="K279">
+        <v>371</v>
+      </c>
+      <c r="L279">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>2011</v>
       </c>
@@ -7022,8 +9746,35 @@
       <c r="C280" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D280">
+        <v>1793</v>
+      </c>
+      <c r="E280">
+        <v>2236</v>
+      </c>
+      <c r="F280">
+        <v>560</v>
+      </c>
+      <c r="G280">
+        <v>873</v>
+      </c>
+      <c r="H280">
+        <v>1531</v>
+      </c>
+      <c r="I280">
+        <v>64</v>
+      </c>
+      <c r="J280">
+        <v>1068</v>
+      </c>
+      <c r="K280">
+        <v>94</v>
+      </c>
+      <c r="L280">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2011</v>
       </c>
@@ -7033,8 +9784,32 @@
       <c r="C281" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D281">
+        <v>233</v>
+      </c>
+      <c r="E281">
+        <v>135</v>
+      </c>
+      <c r="F281">
+        <v>20</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>281</v>
+      </c>
+      <c r="J281">
+        <v>104</v>
+      </c>
+      <c r="K281">
+        <v>10</v>
+      </c>
+      <c r="L281">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2012</v>
       </c>
@@ -7045,7 +9820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2012</v>
       </c>
@@ -7056,7 +9831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2012</v>
       </c>
@@ -7067,7 +9842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>2012</v>
       </c>
@@ -7078,7 +9853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>2012</v>
       </c>
@@ -7089,7 +9864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>2012</v>
       </c>
@@ -7100,7 +9875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>2012</v>
       </c>
@@ -15043,7 +17818,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J1009">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1009">
     <sortCondition ref="A2:A1009"/>
     <sortCondition ref="C2:C1009"/>
   </sortState>
